--- a/ROSA_vitaSPEC/Results/test_pretraitements/trans.beta.carotenes/Resultats_trans.beta.carotenes_moy_ADJR2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/trans.beta.carotenes/Resultats_trans.beta.carotenes_moy_ADJR2.xlsx
@@ -211,7 +211,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,13 +223,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -255,108 +248,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -659,7 +560,9 @@
   <dimension ref="A1:P47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.7109375" customWidth="1"/>
+    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="16" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -717,49 +620,49 @@
         <v>16</v>
       </c>
       <c r="B2">
-        <v>0.33551529476999192</v>
+        <v>0.33600596974602331</v>
       </c>
       <c r="C2">
-        <v>0.47838662339313148</v>
+        <v>0.48215333580767539</v>
       </c>
       <c r="D2">
-        <v>0.50146343658818182</v>
+        <v>0.50538712527943852</v>
       </c>
       <c r="E2">
-        <v>0.53000750260659546</v>
+        <v>0.53098784773864838</v>
       </c>
       <c r="F2">
-        <v>0.51939958079351656</v>
+        <v>0.51809585601972741</v>
       </c>
       <c r="G2">
-        <v>0.52865354479677396</v>
+        <v>0.53363408493219355</v>
       </c>
       <c r="H2">
-        <v>0.52331104714363386</v>
+        <v>0.5277387494100948</v>
       </c>
       <c r="I2">
-        <v>0.5220530998211681</v>
+        <v>0.52592910243753854</v>
       </c>
       <c r="J2">
-        <v>0.52850004453780663</v>
+        <v>0.52890108971948846</v>
       </c>
       <c r="K2">
-        <v>0.52144776308787677</v>
+        <v>0.52562039990743559</v>
       </c>
       <c r="L2">
-        <v>0.48540734117631512</v>
+        <v>0.48934039420253272</v>
       </c>
       <c r="M2">
-        <v>0.45010273923740801</v>
+        <v>0.45104360788558778</v>
       </c>
       <c r="N2">
-        <v>0.41673068731076129</v>
+        <v>0.4191487725345005</v>
       </c>
       <c r="O2">
-        <v>0.37132588674858691</v>
+        <v>0.37039663785206067</v>
       </c>
       <c r="P2">
-        <v>0.40587715698549798</v>
+        <v>0.40441243121599008</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -767,49 +670,49 @@
         <v>17</v>
       </c>
       <c r="B3">
-        <v>0.43735459569422691</v>
+        <v>0.43643307274762527</v>
       </c>
       <c r="C3">
-        <v>0.4965975654568513</v>
+        <v>0.49710430618553808</v>
       </c>
       <c r="D3">
-        <v>0.49113178802247148</v>
+        <v>0.49314014236650328</v>
       </c>
       <c r="E3">
-        <v>0.50014032801206953</v>
+        <v>0.50305764492731941</v>
       </c>
       <c r="F3">
-        <v>0.50017896423125308</v>
+        <v>0.50395960905542958</v>
       </c>
       <c r="G3">
-        <v>0.50586351869196522</v>
+        <v>0.51385482468392651</v>
       </c>
       <c r="H3">
-        <v>0.47344281314256381</v>
+        <v>0.48065623280606301</v>
       </c>
       <c r="I3">
-        <v>0.46495283207517879</v>
+        <v>0.46852431402543793</v>
       </c>
       <c r="J3">
-        <v>0.44866367210492852</v>
+        <v>0.45159382875109799</v>
       </c>
       <c r="K3">
-        <v>0.43159332108018011</v>
+        <v>0.43315180553543547</v>
       </c>
       <c r="L3">
-        <v>0.39384020198076469</v>
+        <v>0.39700224947554857</v>
       </c>
       <c r="M3">
-        <v>0.30997975180669363</v>
+        <v>0.31824143819712031</v>
       </c>
       <c r="N3">
-        <v>0.22253575054193989</v>
+        <v>0.2326443521762368</v>
       </c>
       <c r="O3">
-        <v>0.1730402008177713</v>
+        <v>0.179548282138319</v>
       </c>
       <c r="P3">
-        <v>0.1170443651241056</v>
+        <v>0.11767619753732091</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -817,49 +720,49 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>0.35168107519420599</v>
+        <v>0.35762896617122047</v>
       </c>
       <c r="C4">
-        <v>0.47098017182504298</v>
+        <v>0.47565325435307498</v>
       </c>
       <c r="D4">
-        <v>0.48219553792115499</v>
+        <v>0.48835775097321232</v>
       </c>
       <c r="E4">
-        <v>0.47715770615181219</v>
+        <v>0.48462497113940761</v>
       </c>
       <c r="F4">
-        <v>0.5024645292900517</v>
+        <v>0.5143558208348169</v>
       </c>
       <c r="G4">
-        <v>0.54464384616880646</v>
+        <v>0.55630038713721197</v>
       </c>
       <c r="H4">
-        <v>0.56194466620425665</v>
+        <v>0.57078544667301712</v>
       </c>
       <c r="I4">
-        <v>0.52441233026660294</v>
+        <v>0.53601508258965658</v>
       </c>
       <c r="J4">
-        <v>0.47922993594984059</v>
+        <v>0.49122019440838199</v>
       </c>
       <c r="K4">
-        <v>0.45307292607498928</v>
+        <v>0.45911302894855449</v>
       </c>
       <c r="L4">
-        <v>0.36932347046482078</v>
+        <v>0.37941888038126248</v>
       </c>
       <c r="M4">
-        <v>0.38084036534991222</v>
+        <v>0.38776828167488481</v>
       </c>
       <c r="N4">
-        <v>0.42020262094101329</v>
+        <v>0.42689327147882211</v>
       </c>
       <c r="O4">
-        <v>0.44415379385161557</v>
+        <v>0.45277679518993352</v>
       </c>
       <c r="P4">
-        <v>0.44572415352295458</v>
+        <v>0.45571125944701019</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -867,49 +770,49 @@
         <v>19</v>
       </c>
       <c r="B5">
-        <v>0.48819195627404388</v>
+        <v>0.48815911964664999</v>
       </c>
       <c r="C5">
-        <v>0.49293531919837308</v>
+        <v>0.49315046738336082</v>
       </c>
       <c r="D5">
-        <v>0.50072229431296689</v>
+        <v>0.49956090371780271</v>
       </c>
       <c r="E5">
-        <v>0.52085364372102805</v>
+        <v>0.5231374757453594</v>
       </c>
       <c r="F5">
-        <v>0.51688298191714543</v>
+        <v>0.51755068374100199</v>
       </c>
       <c r="G5">
-        <v>0.5233361133811496</v>
+        <v>0.52356338476102615</v>
       </c>
       <c r="H5">
-        <v>0.5231143769437685</v>
+        <v>0.5215421262895007</v>
       </c>
       <c r="I5">
-        <v>0.49488869263694851</v>
+        <v>0.48965290518510313</v>
       </c>
       <c r="J5">
-        <v>0.46042644777868003</v>
+        <v>0.45634274227976918</v>
       </c>
       <c r="K5">
-        <v>0.41904765177367831</v>
+        <v>0.416936751507194</v>
       </c>
       <c r="L5">
-        <v>0.39523513285151812</v>
+        <v>0.38110828131084512</v>
       </c>
       <c r="M5">
-        <v>0.37894050780871269</v>
+        <v>0.36617289409415571</v>
       </c>
       <c r="N5">
-        <v>0.40402092302647857</v>
+        <v>0.39512190423081178</v>
       </c>
       <c r="O5">
-        <v>0.41553317134927159</v>
+        <v>0.40153174573112388</v>
       </c>
       <c r="P5">
-        <v>0.43084364139459591</v>
+        <v>0.42338442594178688</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -917,49 +820,49 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <v>0.4887675767589082</v>
+        <v>0.49165493334850358</v>
       </c>
       <c r="C6">
-        <v>0.49120103854105768</v>
+        <v>0.49582398781431292</v>
       </c>
       <c r="D6">
-        <v>0.49721234135886161</v>
+        <v>0.50156272993811968</v>
       </c>
       <c r="E6">
-        <v>0.50804241585460619</v>
+        <v>0.51137873657114608</v>
       </c>
       <c r="F6">
-        <v>0.54216554808820394</v>
+        <v>0.54052224963128437</v>
       </c>
       <c r="G6">
-        <v>0.52400903548933342</v>
+        <v>0.5252368291509526</v>
       </c>
       <c r="H6">
-        <v>0.51811007249378505</v>
+        <v>0.51691463362043111</v>
       </c>
       <c r="I6">
-        <v>0.4699876418229052</v>
+        <v>0.46945158699888129</v>
       </c>
       <c r="J6">
-        <v>0.42375946394714981</v>
+        <v>0.42395920841492313</v>
       </c>
       <c r="K6">
-        <v>0.39938499951451789</v>
+        <v>0.39778426425289809</v>
       </c>
       <c r="L6">
-        <v>0.36339478310953299</v>
+        <v>0.3642497142788651</v>
       </c>
       <c r="M6">
-        <v>0.36049368407068039</v>
+        <v>0.36291833799662709</v>
       </c>
       <c r="N6">
-        <v>0.34680797885122638</v>
+        <v>0.34666652289401051</v>
       </c>
       <c r="O6">
-        <v>0.36964615830328962</v>
+        <v>0.36732427747739149</v>
       </c>
       <c r="P6">
-        <v>0.37225489057568489</v>
+        <v>0.37772087141620603</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -967,49 +870,49 @@
         <v>21</v>
       </c>
       <c r="B7">
-        <v>0.35248971389182382</v>
+        <v>0.35285322087333187</v>
       </c>
       <c r="C7">
-        <v>0.48409063526611817</v>
+        <v>0.48488361063472851</v>
       </c>
       <c r="D7">
-        <v>0.54526885450773865</v>
+        <v>0.5424661021081103</v>
       </c>
       <c r="E7">
-        <v>0.58077156775327088</v>
+        <v>0.57790225645532001</v>
       </c>
       <c r="F7">
-        <v>0.58749210132079233</v>
+        <v>0.58398132044460038</v>
       </c>
       <c r="G7">
-        <v>0.58508827969098354</v>
+        <v>0.58294463166668453</v>
       </c>
       <c r="H7">
-        <v>0.5727327997910403</v>
+        <v>0.57361971397751632</v>
       </c>
       <c r="I7">
-        <v>0.57456177999121227</v>
+        <v>0.577406567778871</v>
       </c>
       <c r="J7">
-        <v>0.54074123728317658</v>
+        <v>0.54388166033043805</v>
       </c>
       <c r="K7">
-        <v>0.49245461364223758</v>
+        <v>0.50202072942855991</v>
       </c>
       <c r="L7">
-        <v>0.46730411610934919</v>
+        <v>0.47633201942183179</v>
       </c>
       <c r="M7">
-        <v>0.43050777044685951</v>
+        <v>0.43753350105739902</v>
       </c>
       <c r="N7">
-        <v>0.42754129837192772</v>
+        <v>0.43708029813230481</v>
       </c>
       <c r="O7">
-        <v>0.4517044589722895</v>
+        <v>0.46055909892464669</v>
       </c>
       <c r="P7">
-        <v>0.46745215255148809</v>
+        <v>0.47856457611317482</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -1017,49 +920,49 @@
         <v>22</v>
       </c>
       <c r="B8">
-        <v>0.40243627607478782</v>
+        <v>0.4001474805298928</v>
       </c>
       <c r="C8">
-        <v>0.46637792952357748</v>
+        <v>0.46572511602997102</v>
       </c>
       <c r="D8">
-        <v>0.52105950569532766</v>
+        <v>0.51890113435071505</v>
       </c>
       <c r="E8">
-        <v>0.52849304433994249</v>
+        <v>0.52675271155904047</v>
       </c>
       <c r="F8">
-        <v>0.53218591873046328</v>
+        <v>0.53041777114567634</v>
       </c>
       <c r="G8">
-        <v>0.53041577626765279</v>
+        <v>0.52992277955474998</v>
       </c>
       <c r="H8">
-        <v>0.54577576305246978</v>
+        <v>0.54228544919168775</v>
       </c>
       <c r="I8">
-        <v>0.52682850610842447</v>
+        <v>0.52396689574732669</v>
       </c>
       <c r="J8">
-        <v>0.48959345808379751</v>
+        <v>0.49117868007983773</v>
       </c>
       <c r="K8">
-        <v>0.43161886570778851</v>
+        <v>0.43273720032675772</v>
       </c>
       <c r="L8">
-        <v>0.38264601509494411</v>
+        <v>0.38239897177012599</v>
       </c>
       <c r="M8">
-        <v>0.38726077405236359</v>
+        <v>0.38317543229012102</v>
       </c>
       <c r="N8">
-        <v>0.41950302314743709</v>
+        <v>0.41521346830214079</v>
       </c>
       <c r="O8">
-        <v>0.44863572959411879</v>
+        <v>0.44240189446850842</v>
       </c>
       <c r="P8">
-        <v>0.43089739796143328</v>
+        <v>0.4242527875675462</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -1067,49 +970,49 @@
         <v>23</v>
       </c>
       <c r="B9">
-        <v>0.40392493086233727</v>
+        <v>0.40466270587506592</v>
       </c>
       <c r="C9">
-        <v>0.46743361361249203</v>
+        <v>0.47039360496984578</v>
       </c>
       <c r="D9">
-        <v>0.51766051603217911</v>
+        <v>0.5233909198492166</v>
       </c>
       <c r="E9">
-        <v>0.52349436146548745</v>
+        <v>0.5294246398178053</v>
       </c>
       <c r="F9">
-        <v>0.52573430082254013</v>
+        <v>0.53130741491307154</v>
       </c>
       <c r="G9">
-        <v>0.52194689978238051</v>
+        <v>0.5260768164709263</v>
       </c>
       <c r="H9">
-        <v>0.53538175703721413</v>
+        <v>0.53988403822109421</v>
       </c>
       <c r="I9">
-        <v>0.52219834725003089</v>
+        <v>0.52410539825282954</v>
       </c>
       <c r="J9">
-        <v>0.50351830928093066</v>
+        <v>0.50896938202655406</v>
       </c>
       <c r="K9">
-        <v>0.4693359319792646</v>
+        <v>0.47579084800895421</v>
       </c>
       <c r="L9">
-        <v>0.41664472066439689</v>
+        <v>0.42841038809694232</v>
       </c>
       <c r="M9">
-        <v>0.41695785588847267</v>
+        <v>0.42777514958518881</v>
       </c>
       <c r="N9">
-        <v>0.45783640171350459</v>
+        <v>0.46301590204549509</v>
       </c>
       <c r="O9">
-        <v>0.49292296277875702</v>
+        <v>0.49383939707327063</v>
       </c>
       <c r="P9">
-        <v>0.47017388972043211</v>
+        <v>0.47421022215591069</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -1117,49 +1020,49 @@
         <v>24</v>
       </c>
       <c r="B10">
-        <v>0.40195076370232241</v>
+        <v>0.39926159444176612</v>
       </c>
       <c r="C10">
-        <v>0.46697897557878648</v>
+        <v>0.46037356633938992</v>
       </c>
       <c r="D10">
-        <v>0.51683523573624712</v>
+        <v>0.51461924672822679</v>
       </c>
       <c r="E10">
-        <v>0.52301283679144828</v>
+        <v>0.51853270570402665</v>
       </c>
       <c r="F10">
-        <v>0.52489897836764321</v>
+        <v>0.52040123289649332</v>
       </c>
       <c r="G10">
-        <v>0.51984066215064151</v>
+        <v>0.51696176367577618</v>
       </c>
       <c r="H10">
-        <v>0.53286197334143226</v>
+        <v>0.53216000814848063</v>
       </c>
       <c r="I10">
-        <v>0.5232581820764578</v>
+        <v>0.51923743736160821</v>
       </c>
       <c r="J10">
-        <v>0.50264188029107526</v>
+        <v>0.50207598675056408</v>
       </c>
       <c r="K10">
-        <v>0.47586747209893893</v>
+        <v>0.47423267401986058</v>
       </c>
       <c r="L10">
-        <v>0.42340954186267538</v>
+        <v>0.42679159498852381</v>
       </c>
       <c r="M10">
-        <v>0.42339371158688649</v>
+        <v>0.42502154064543912</v>
       </c>
       <c r="N10">
-        <v>0.45958114877149442</v>
+        <v>0.45605455015724528</v>
       </c>
       <c r="O10">
-        <v>0.49386578814782778</v>
+        <v>0.4903762124327522</v>
       </c>
       <c r="P10">
-        <v>0.47315023097203052</v>
+        <v>0.47096688949766929</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -1167,49 +1070,49 @@
         <v>25</v>
       </c>
       <c r="B11">
-        <v>0.4041047454752526</v>
+        <v>0.40651154959852892</v>
       </c>
       <c r="C11">
-        <v>0.46770486443633602</v>
+        <v>0.47229019369322528</v>
       </c>
       <c r="D11">
-        <v>0.52095979493831113</v>
+        <v>0.52524740911081647</v>
       </c>
       <c r="E11">
-        <v>0.52771237726226128</v>
+        <v>0.53277923459912979</v>
       </c>
       <c r="F11">
-        <v>0.52960460847861568</v>
+        <v>0.53479804354606031</v>
       </c>
       <c r="G11">
-        <v>0.52722136598373204</v>
+        <v>0.53216968210152071</v>
       </c>
       <c r="H11">
-        <v>0.54071529311081534</v>
+        <v>0.54494583156955401</v>
       </c>
       <c r="I11">
-        <v>0.52811078499651065</v>
+        <v>0.53275405832290279</v>
       </c>
       <c r="J11">
-        <v>0.51015185397249951</v>
+        <v>0.51518505528863345</v>
       </c>
       <c r="K11">
-        <v>0.47404661831947209</v>
+        <v>0.47844246230318749</v>
       </c>
       <c r="L11">
-        <v>0.4186215218077009</v>
+        <v>0.42047365165354877</v>
       </c>
       <c r="M11">
-        <v>0.42034143126350099</v>
+        <v>0.41640694407355883</v>
       </c>
       <c r="N11">
-        <v>0.4589177530607042</v>
+        <v>0.45407920673150137</v>
       </c>
       <c r="O11">
-        <v>0.49200917961872731</v>
+        <v>0.48914995074402939</v>
       </c>
       <c r="P11">
-        <v>0.48622257209900738</v>
+        <v>0.47942382127043648</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -1217,49 +1120,49 @@
         <v>26</v>
       </c>
       <c r="B12">
-        <v>0.49575032354534898</v>
+        <v>0.49490970542930779</v>
       </c>
       <c r="C12">
-        <v>0.50666601906025177</v>
+        <v>0.50513996723538956</v>
       </c>
       <c r="D12">
-        <v>0.53271664684499509</v>
+        <v>0.53193915402755421</v>
       </c>
       <c r="E12">
-        <v>0.55409965441163256</v>
+        <v>0.55617642261615108</v>
       </c>
       <c r="F12">
-        <v>0.55775416646490195</v>
+        <v>0.55961532921881607</v>
       </c>
       <c r="G12">
-        <v>0.55801146488268716</v>
+        <v>0.5589331292325338</v>
       </c>
       <c r="H12">
-        <v>0.55077265458034186</v>
+        <v>0.55408654256871348</v>
       </c>
       <c r="I12">
-        <v>0.52851265596059394</v>
+        <v>0.52980854500105323</v>
       </c>
       <c r="J12">
-        <v>0.49137767087022338</v>
+        <v>0.49092245394569167</v>
       </c>
       <c r="K12">
-        <v>0.44009558079296612</v>
+        <v>0.44015928013943201</v>
       </c>
       <c r="L12">
-        <v>0.3880347214787403</v>
+        <v>0.38779411060456581</v>
       </c>
       <c r="M12">
-        <v>0.35724391381116449</v>
+        <v>0.35157900308503942</v>
       </c>
       <c r="N12">
-        <v>0.36816088571203259</v>
+        <v>0.36329038113223538</v>
       </c>
       <c r="O12">
-        <v>0.37744601066331068</v>
+        <v>0.37727463772755843</v>
       </c>
       <c r="P12">
-        <v>0.3733785397627527</v>
+        <v>0.3676609747453477</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -1267,49 +1170,49 @@
         <v>27</v>
       </c>
       <c r="B13">
-        <v>0.49538756323009647</v>
+        <v>0.49560192810780329</v>
       </c>
       <c r="C13">
-        <v>0.50627312310897343</v>
+        <v>0.5066523459620037</v>
       </c>
       <c r="D13">
-        <v>0.51735604352817177</v>
+        <v>0.51580277711700795</v>
       </c>
       <c r="E13">
-        <v>0.52853718171801345</v>
+        <v>0.52675921984341456</v>
       </c>
       <c r="F13">
-        <v>0.53534754520118832</v>
+        <v>0.5355206648777856</v>
       </c>
       <c r="G13">
-        <v>0.52579796904607057</v>
+        <v>0.5277497684017205</v>
       </c>
       <c r="H13">
-        <v>0.5202940649466874</v>
+        <v>0.52340963464355084</v>
       </c>
       <c r="I13">
-        <v>0.4939362121955202</v>
+        <v>0.49600390312273152</v>
       </c>
       <c r="J13">
-        <v>0.46986607729440599</v>
+        <v>0.47027654395246049</v>
       </c>
       <c r="K13">
-        <v>0.41553682013925242</v>
+        <v>0.41381476040639248</v>
       </c>
       <c r="L13">
-        <v>0.39212746207641369</v>
+        <v>0.38768556017110212</v>
       </c>
       <c r="M13">
-        <v>0.37658641932685161</v>
+        <v>0.3690183916520422</v>
       </c>
       <c r="N13">
-        <v>0.35441852692578318</v>
+        <v>0.3424736321764828</v>
       </c>
       <c r="O13">
-        <v>0.32409031947856831</v>
+        <v>0.31285381746273933</v>
       </c>
       <c r="P13">
-        <v>0.28120934008281201</v>
+        <v>0.2575961903929046</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -1317,49 +1220,49 @@
         <v>28</v>
       </c>
       <c r="B14">
-        <v>0.35301326961048862</v>
+        <v>0.35475792977148329</v>
       </c>
       <c r="C14">
-        <v>0.48394070191142702</v>
+        <v>0.48666370982536189</v>
       </c>
       <c r="D14">
-        <v>0.54001856430428596</v>
+        <v>0.54574281065926367</v>
       </c>
       <c r="E14">
-        <v>0.57696144026356566</v>
+        <v>0.58059993376760988</v>
       </c>
       <c r="F14">
-        <v>0.58220800037407305</v>
+        <v>0.58680497570347212</v>
       </c>
       <c r="G14">
-        <v>0.57846714543184374</v>
+        <v>0.58620030018611369</v>
       </c>
       <c r="H14">
-        <v>0.57071120386223617</v>
+        <v>0.57533907088765934</v>
       </c>
       <c r="I14">
-        <v>0.57585341174704707</v>
+        <v>0.58033909003291839</v>
       </c>
       <c r="J14">
-        <v>0.54714589656491608</v>
+        <v>0.55616150729256653</v>
       </c>
       <c r="K14">
-        <v>0.51028675438637539</v>
+        <v>0.5157735644783169</v>
       </c>
       <c r="L14">
-        <v>0.49605108215531402</v>
+        <v>0.50298439884575141</v>
       </c>
       <c r="M14">
-        <v>0.46461276322376188</v>
+        <v>0.46849219096248118</v>
       </c>
       <c r="N14">
-        <v>0.46154771589088389</v>
+        <v>0.4591749265927666</v>
       </c>
       <c r="O14">
-        <v>0.47778190986351021</v>
+        <v>0.47359080024285072</v>
       </c>
       <c r="P14">
-        <v>0.5032694455970772</v>
+        <v>0.50304071419093044</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -1367,49 +1270,49 @@
         <v>29</v>
       </c>
       <c r="B15">
-        <v>0.35089788815484951</v>
+        <v>0.35438062459399677</v>
       </c>
       <c r="C15">
-        <v>0.48175698482335322</v>
+        <v>0.48605392175920342</v>
       </c>
       <c r="D15">
-        <v>0.54015824656554234</v>
+        <v>0.54527993402859043</v>
       </c>
       <c r="E15">
-        <v>0.57858238580973964</v>
+        <v>0.57877593377067038</v>
       </c>
       <c r="F15">
-        <v>0.58403013124995939</v>
+        <v>0.58551268950375768</v>
       </c>
       <c r="G15">
-        <v>0.58125553298364441</v>
+        <v>0.58309462351512342</v>
       </c>
       <c r="H15">
-        <v>0.57228882695582051</v>
+        <v>0.57595651091593592</v>
       </c>
       <c r="I15">
-        <v>0.57579453679428894</v>
+        <v>0.57952664943727505</v>
       </c>
       <c r="J15">
-        <v>0.54974214354268502</v>
+        <v>0.55645704145302954</v>
       </c>
       <c r="K15">
-        <v>0.50917623906553966</v>
+        <v>0.5179164452388676</v>
       </c>
       <c r="L15">
-        <v>0.49550936295149228</v>
+        <v>0.51237475738040517</v>
       </c>
       <c r="M15">
-        <v>0.46031156943680818</v>
+        <v>0.47734129618657739</v>
       </c>
       <c r="N15">
-        <v>0.45642449514873029</v>
+        <v>0.47292050065195501</v>
       </c>
       <c r="O15">
-        <v>0.47206421341210009</v>
+        <v>0.48592850218077271</v>
       </c>
       <c r="P15">
-        <v>0.49597007251880731</v>
+        <v>0.51237542885772303</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -1417,49 +1320,49 @@
         <v>30</v>
       </c>
       <c r="B16">
-        <v>0.35416101269398331</v>
+        <v>0.35623579000014871</v>
       </c>
       <c r="C16">
-        <v>0.48640757376067228</v>
+        <v>0.48731535433126749</v>
       </c>
       <c r="D16">
-        <v>0.54745211819075879</v>
+        <v>0.54733022178458335</v>
       </c>
       <c r="E16">
-        <v>0.58171050989720996</v>
+        <v>0.58292793730122994</v>
       </c>
       <c r="F16">
-        <v>0.58802104149111845</v>
+        <v>0.59003713263886759</v>
       </c>
       <c r="G16">
-        <v>0.58580223601990888</v>
+        <v>0.58519130932475283</v>
       </c>
       <c r="H16">
-        <v>0.57508838725347977</v>
+        <v>0.57891081978782144</v>
       </c>
       <c r="I16">
-        <v>0.57947092028254998</v>
+        <v>0.58127657185598181</v>
       </c>
       <c r="J16">
-        <v>0.55416948595895454</v>
+        <v>0.55770173385664068</v>
       </c>
       <c r="K16">
-        <v>0.51375361044563272</v>
+        <v>0.51892992689645945</v>
       </c>
       <c r="L16">
-        <v>0.50404119990432805</v>
+        <v>0.51121643455713617</v>
       </c>
       <c r="M16">
-        <v>0.47261256891595832</v>
+        <v>0.48244680140896068</v>
       </c>
       <c r="N16">
-        <v>0.45750587744789789</v>
+        <v>0.47302731327631659</v>
       </c>
       <c r="O16">
-        <v>0.4737411819547615</v>
+        <v>0.48032169530718682</v>
       </c>
       <c r="P16">
-        <v>0.49895575710047269</v>
+        <v>0.50199912411170777</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
@@ -1467,49 +1370,49 @@
         <v>31</v>
       </c>
       <c r="B17">
-        <v>0.35559009848210982</v>
+        <v>0.35279564936414848</v>
       </c>
       <c r="C17">
-        <v>0.48606559963435969</v>
+        <v>0.48545197395995943</v>
       </c>
       <c r="D17">
-        <v>0.5433936768291977</v>
+        <v>0.54411137849562419</v>
       </c>
       <c r="E17">
-        <v>0.57855840220913612</v>
+        <v>0.58108444344613885</v>
       </c>
       <c r="F17">
-        <v>0.58308730302937806</v>
+        <v>0.5881856211337616</v>
       </c>
       <c r="G17">
-        <v>0.58064913469875212</v>
+        <v>0.5851174379201014</v>
       </c>
       <c r="H17">
-        <v>0.57022511011700849</v>
+        <v>0.57669548271208027</v>
       </c>
       <c r="I17">
-        <v>0.57570984255404822</v>
+        <v>0.58185446801967011</v>
       </c>
       <c r="J17">
-        <v>0.54998262509019502</v>
+        <v>0.55722208185773847</v>
       </c>
       <c r="K17">
-        <v>0.51184554183901898</v>
+        <v>0.52027871963310168</v>
       </c>
       <c r="L17">
-        <v>0.50206250134557784</v>
+        <v>0.51230732134697121</v>
       </c>
       <c r="M17">
-        <v>0.47227603950597818</v>
+        <v>0.49411815397791409</v>
       </c>
       <c r="N17">
-        <v>0.46426995255941511</v>
+        <v>0.48755082833233132</v>
       </c>
       <c r="O17">
-        <v>0.4821437572732295</v>
+        <v>0.50641774158651554</v>
       </c>
       <c r="P17">
-        <v>0.50226324974106962</v>
+        <v>0.52092226822286158</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -1517,49 +1420,49 @@
         <v>32</v>
       </c>
       <c r="B18">
-        <v>0.49861962439958579</v>
+        <v>0.49766482961425829</v>
       </c>
       <c r="C18">
-        <v>0.50397411515556689</v>
+        <v>0.50590793241966192</v>
       </c>
       <c r="D18">
-        <v>0.52599837183033638</v>
+        <v>0.52957214511646233</v>
       </c>
       <c r="E18">
-        <v>0.55203067364509673</v>
+        <v>0.55464464744211517</v>
       </c>
       <c r="F18">
-        <v>0.56084735547206277</v>
+        <v>0.56508405795366579</v>
       </c>
       <c r="G18">
-        <v>0.55780189786392531</v>
+        <v>0.56141873043664892</v>
       </c>
       <c r="H18">
-        <v>0.55367441455926658</v>
+        <v>0.55798731946878466</v>
       </c>
       <c r="I18">
-        <v>0.51187469030819421</v>
+        <v>0.51619580350991101</v>
       </c>
       <c r="J18">
-        <v>0.50224029710475981</v>
+        <v>0.5047576979923577</v>
       </c>
       <c r="K18">
-        <v>0.46024406713046412</v>
+        <v>0.45905623868199757</v>
       </c>
       <c r="L18">
-        <v>0.43220010310947288</v>
+        <v>0.43236296480229552</v>
       </c>
       <c r="M18">
-        <v>0.42227750570407829</v>
+        <v>0.42249309700915189</v>
       </c>
       <c r="N18">
-        <v>0.44388882515464678</v>
+        <v>0.44364593556582849</v>
       </c>
       <c r="O18">
-        <v>0.45458387850536902</v>
+        <v>0.45369180300398382</v>
       </c>
       <c r="P18">
-        <v>0.4595886305436031</v>
+        <v>0.46399151468732103</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -1567,49 +1470,49 @@
         <v>33</v>
       </c>
       <c r="B19">
-        <v>0.50062970355655878</v>
+        <v>0.49822911122100072</v>
       </c>
       <c r="C19">
-        <v>0.50667532115151059</v>
+        <v>0.50262951602884054</v>
       </c>
       <c r="D19">
-        <v>0.52085811083174161</v>
+        <v>0.51694935295499622</v>
       </c>
       <c r="E19">
-        <v>0.54104670321158288</v>
+        <v>0.53503978995256884</v>
       </c>
       <c r="F19">
-        <v>0.5686720702458431</v>
+        <v>0.56197563807459161</v>
       </c>
       <c r="G19">
-        <v>0.56158364665733596</v>
+        <v>0.55181411245406009</v>
       </c>
       <c r="H19">
-        <v>0.55329748614185437</v>
+        <v>0.53943985125112759</v>
       </c>
       <c r="I19">
-        <v>0.52416795135193972</v>
+        <v>0.50814878823792464</v>
       </c>
       <c r="J19">
-        <v>0.47334354333696832</v>
+        <v>0.45671265820374851</v>
       </c>
       <c r="K19">
-        <v>0.44933517051030453</v>
+        <v>0.43271761569210421</v>
       </c>
       <c r="L19">
-        <v>0.42748360118106588</v>
+        <v>0.4122748761783554</v>
       </c>
       <c r="M19">
-        <v>0.43766829259411949</v>
+        <v>0.42325429171699641</v>
       </c>
       <c r="N19">
-        <v>0.44163124608301529</v>
+        <v>0.43075027936201599</v>
       </c>
       <c r="O19">
-        <v>0.45450277699351999</v>
+        <v>0.44394870340287967</v>
       </c>
       <c r="P19">
-        <v>0.44162817866433252</v>
+        <v>0.4277619532738674</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -1617,49 +1520,49 @@
         <v>34</v>
       </c>
       <c r="B20">
-        <v>0.50342072788102388</v>
+        <v>0.50033358770074965</v>
       </c>
       <c r="C20">
-        <v>0.51105288940314497</v>
+        <v>0.50386341848171912</v>
       </c>
       <c r="D20">
-        <v>0.53517599714161235</v>
+        <v>0.52527284810121788</v>
       </c>
       <c r="E20">
-        <v>0.55201853250721966</v>
+        <v>0.54071433159488624</v>
       </c>
       <c r="F20">
-        <v>0.56379093140315995</v>
+        <v>0.55472244862230835</v>
       </c>
       <c r="G20">
-        <v>0.56476571341179072</v>
+        <v>0.55862550192771043</v>
       </c>
       <c r="H20">
-        <v>0.54205048924919075</v>
+        <v>0.53584297634468825</v>
       </c>
       <c r="I20">
-        <v>0.52245129818292257</v>
+        <v>0.51347828125781125</v>
       </c>
       <c r="J20">
-        <v>0.46868577718394</v>
+        <v>0.46139725086511041</v>
       </c>
       <c r="K20">
-        <v>0.43184171266950272</v>
+        <v>0.42965215568317422</v>
       </c>
       <c r="L20">
-        <v>0.44361841832621801</v>
+        <v>0.44271585520344708</v>
       </c>
       <c r="M20">
-        <v>0.46520933986216889</v>
+        <v>0.47007309728029451</v>
       </c>
       <c r="N20">
-        <v>0.46218255459394969</v>
+        <v>0.46995795863015538</v>
       </c>
       <c r="O20">
-        <v>0.49473478351484718</v>
+        <v>0.50259156675826366</v>
       </c>
       <c r="P20">
-        <v>0.4751629404036698</v>
+        <v>0.4805487972466132</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
@@ -1667,49 +1570,49 @@
         <v>35</v>
       </c>
       <c r="B21">
-        <v>0.43765702378569038</v>
+        <v>0.43536736033423301</v>
       </c>
       <c r="C21">
-        <v>0.49431813252270412</v>
+        <v>0.49455280111675759</v>
       </c>
       <c r="D21">
-        <v>0.49361005546118719</v>
+        <v>0.49677249633805892</v>
       </c>
       <c r="E21">
-        <v>0.50961609026884302</v>
+        <v>0.51688845433305108</v>
       </c>
       <c r="F21">
-        <v>0.52368228541206774</v>
+        <v>0.53167901538914231</v>
       </c>
       <c r="G21">
-        <v>0.5257240143936176</v>
+        <v>0.53091618807612972</v>
       </c>
       <c r="H21">
-        <v>0.45433651692335891</v>
+        <v>0.46637486640099041</v>
       </c>
       <c r="I21">
-        <v>0.42344104002024369</v>
+        <v>0.43280433453757611</v>
       </c>
       <c r="J21">
-        <v>0.41638001329853508</v>
+        <v>0.41572424920957468</v>
       </c>
       <c r="K21">
-        <v>0.37870847075493991</v>
+        <v>0.38054779923942789</v>
       </c>
       <c r="L21">
-        <v>0.34911008255668541</v>
+        <v>0.35068171848744278</v>
       </c>
       <c r="M21">
-        <v>0.28602759900860608</v>
+        <v>0.29194896498051481</v>
       </c>
       <c r="N21">
-        <v>0.23115053094674751</v>
+        <v>0.23837985719668039</v>
       </c>
       <c r="O21">
-        <v>0.1661224224959931</v>
+        <v>0.17176514278643071</v>
       </c>
       <c r="P21">
-        <v>5.4150923036756789E-2</v>
+        <v>6.3463795498211059E-2</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -1717,49 +1620,49 @@
         <v>36</v>
       </c>
       <c r="B22">
-        <v>0.43595248387303559</v>
+        <v>0.43744705652928539</v>
       </c>
       <c r="C22">
-        <v>0.49332728653776081</v>
+        <v>0.49477211643924601</v>
       </c>
       <c r="D22">
-        <v>0.49304422496667177</v>
+        <v>0.49370110983693238</v>
       </c>
       <c r="E22">
-        <v>0.51314667606815723</v>
+        <v>0.51163264376015638</v>
       </c>
       <c r="F22">
-        <v>0.52885003350913928</v>
+        <v>0.52605474085369175</v>
       </c>
       <c r="G22">
-        <v>0.54449978133991295</v>
+        <v>0.54089445403358472</v>
       </c>
       <c r="H22">
-        <v>0.47604752501094322</v>
+        <v>0.46671425211563128</v>
       </c>
       <c r="I22">
-        <v>0.4482565282330413</v>
+        <v>0.43928725144600989</v>
       </c>
       <c r="J22">
-        <v>0.43751215521209991</v>
+        <v>0.42927326020173601</v>
       </c>
       <c r="K22">
-        <v>0.40927279686333973</v>
+        <v>0.40806659980339499</v>
       </c>
       <c r="L22">
-        <v>0.36773319707935481</v>
+        <v>0.36318365349405202</v>
       </c>
       <c r="M22">
-        <v>0.30812185171472378</v>
+        <v>0.30496744431658579</v>
       </c>
       <c r="N22">
-        <v>0.27516504157860672</v>
+        <v>0.26764167351960377</v>
       </c>
       <c r="O22">
-        <v>0.20057776278457251</v>
+        <v>0.1918492124320279</v>
       </c>
       <c r="P22">
-        <v>0.10247615751806829</v>
+        <v>8.9350052964228974E-2</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
@@ -1767,49 +1670,49 @@
         <v>37</v>
       </c>
       <c r="B23">
-        <v>0.49283126533660587</v>
+        <v>0.49268337708515669</v>
       </c>
       <c r="C23">
-        <v>0.49305516846180808</v>
+        <v>0.49281667734417461</v>
       </c>
       <c r="D23">
-        <v>0.52556387384416436</v>
+        <v>0.52787465666737865</v>
       </c>
       <c r="E23">
-        <v>0.53968682209637142</v>
+        <v>0.54005887091947535</v>
       </c>
       <c r="F23">
-        <v>0.50262827244766317</v>
+        <v>0.50380996410798118</v>
       </c>
       <c r="G23">
-        <v>0.39645463324035701</v>
+        <v>0.39775701170860472</v>
       </c>
       <c r="H23">
-        <v>0.34448469832619022</v>
+        <v>0.34610495452842172</v>
       </c>
       <c r="I23">
-        <v>0.33289575601795279</v>
+        <v>0.33273370615979969</v>
       </c>
       <c r="J23">
-        <v>0.28771959947506132</v>
+        <v>0.28856992470763593</v>
       </c>
       <c r="K23">
-        <v>0.235069289217678</v>
+        <v>0.2403864379953739</v>
       </c>
       <c r="L23">
-        <v>0.16852476503883099</v>
+        <v>0.1735650362325685</v>
       </c>
       <c r="M23">
-        <v>8.2362790895220223E-2</v>
+        <v>7.9505318974110659E-2</v>
       </c>
       <c r="N23">
-        <v>-1.985897499033806E-3</v>
+        <v>-5.3390966678262743E-4</v>
       </c>
       <c r="O23">
-        <v>-6.8079559399655043E-2</v>
+        <v>-6.7720237183864621E-2</v>
       </c>
       <c r="P23">
-        <v>-0.1982094041575003</v>
+        <v>-0.19488303264239451</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -1817,49 +1720,49 @@
         <v>38</v>
       </c>
       <c r="B24">
-        <v>0.1326266044757422</v>
+        <v>0.13837930259237111</v>
       </c>
       <c r="C24">
-        <v>0.10643004280221401</v>
+        <v>0.1152352851125017</v>
       </c>
       <c r="D24">
-        <v>0.1555928008732233</v>
+        <v>0.15321988441520079</v>
       </c>
       <c r="E24">
-        <v>7.1331555319956122E-2</v>
+        <v>7.008578801064852E-2</v>
       </c>
       <c r="F24">
-        <v>-7.126291941423181E-2</v>
+        <v>-6.4034759570696126E-2</v>
       </c>
       <c r="G24">
-        <v>-7.8800746011036912E-2</v>
+        <v>-7.2934302228269077E-2</v>
       </c>
       <c r="H24">
-        <v>-0.12515776721459779</v>
+        <v>-0.1128657393739768</v>
       </c>
       <c r="I24">
-        <v>-0.21104426921506159</v>
+        <v>-0.1982713435930179</v>
       </c>
       <c r="J24">
-        <v>-0.28812510263698782</v>
+        <v>-0.26525019003469452</v>
       </c>
       <c r="K24">
-        <v>-0.3003175009759933</v>
+        <v>-0.2828851852444364</v>
       </c>
       <c r="L24">
-        <v>-0.35454366259231002</v>
+        <v>-0.33246225222057368</v>
       </c>
       <c r="M24">
-        <v>-0.3738985389012876</v>
+        <v>-0.35776803469766028</v>
       </c>
       <c r="N24">
-        <v>-0.51242521101674599</v>
+        <v>-0.48358735521531782</v>
       </c>
       <c r="O24">
-        <v>-0.57477981653819454</v>
+        <v>-0.5306892745894608</v>
       </c>
       <c r="P24">
-        <v>-0.63249777914080385</v>
+        <v>-0.57933097108602793</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
@@ -1867,49 +1770,49 @@
         <v>39</v>
       </c>
       <c r="B25">
-        <v>0.1009551505973434</v>
+        <v>0.1004652827545712</v>
       </c>
       <c r="C25">
-        <v>7.7731693938474539E-2</v>
+        <v>8.5707230246005711E-2</v>
       </c>
       <c r="D25">
-        <v>5.5057163167547017E-2</v>
+        <v>6.6474103185907255E-2</v>
       </c>
       <c r="E25">
-        <v>3.6918045738829321E-2</v>
+        <v>4.8635574504234627E-2</v>
       </c>
       <c r="F25">
-        <v>-2.4520193626206919E-3</v>
+        <v>-1.109272623540526E-3</v>
       </c>
       <c r="G25">
-        <v>-0.13841131274190729</v>
+        <v>-0.13368486836823459</v>
       </c>
       <c r="H25">
-        <v>-0.18689911818433819</v>
+        <v>-0.18449271499827721</v>
       </c>
       <c r="I25">
-        <v>-0.25345283358860332</v>
+        <v>-0.25470762883319698</v>
       </c>
       <c r="J25">
-        <v>-0.29992820601123599</v>
+        <v>-0.29934854817146272</v>
       </c>
       <c r="K25">
-        <v>-0.37082372590723511</v>
+        <v>-0.36634852819872182</v>
       </c>
       <c r="L25">
-        <v>-0.44752769819239752</v>
+        <v>-0.44917755682616239</v>
       </c>
       <c r="M25">
-        <v>-0.52295254095039589</v>
+        <v>-0.52811830113693681</v>
       </c>
       <c r="N25">
-        <v>-0.59241827313455631</v>
+        <v>-0.60380110706173451</v>
       </c>
       <c r="O25">
-        <v>-0.64620289303599621</v>
+        <v>-0.66283853935827963</v>
       </c>
       <c r="P25">
-        <v>-0.67807102891824955</v>
+        <v>-0.69657487765616888</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
@@ -1917,49 +1820,49 @@
         <v>40</v>
       </c>
       <c r="B26">
-        <v>0.1017116522900912</v>
+        <v>0.10106822151843051</v>
       </c>
       <c r="C26">
-        <v>8.7336638312200482E-2</v>
+        <v>9.1243734611720279E-2</v>
       </c>
       <c r="D26">
-        <v>0.1008243262550919</v>
+        <v>0.1054587096658214</v>
       </c>
       <c r="E26">
-        <v>9.8116386337839895E-2</v>
+        <v>0.1049842546293431</v>
       </c>
       <c r="F26">
-        <v>3.4829677644921057E-2</v>
+        <v>4.5963514333940733E-2</v>
       </c>
       <c r="G26">
-        <v>-7.6690338786626752E-3</v>
+        <v>2.8290589045167191E-3</v>
       </c>
       <c r="H26">
-        <v>-0.11842520774187271</v>
+        <v>-0.10767749747947671</v>
       </c>
       <c r="I26">
-        <v>-0.14713564130358131</v>
+        <v>-0.14188775452395569</v>
       </c>
       <c r="J26">
-        <v>-0.1011110371948116</v>
+        <v>-9.370487057187521E-2</v>
       </c>
       <c r="K26">
-        <v>-8.1964289197796844E-2</v>
+        <v>-7.9919024466599445E-2</v>
       </c>
       <c r="L26">
-        <v>-0.13164179648125771</v>
+        <v>-0.1208321117747742</v>
       </c>
       <c r="M26">
-        <v>-0.31689486327148048</v>
+        <v>-0.327751488427445</v>
       </c>
       <c r="N26">
-        <v>-0.27085054031891942</v>
+        <v>-0.26908909806025921</v>
       </c>
       <c r="O26">
-        <v>-0.24610638946804109</v>
+        <v>-0.25760458807349851</v>
       </c>
       <c r="P26">
-        <v>-0.25607369926864793</v>
+        <v>-0.24663308592258279</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
@@ -1967,49 +1870,49 @@
         <v>41</v>
       </c>
       <c r="B27">
-        <v>7.5874651619875264E-2</v>
+        <v>7.0310315401076406E-2</v>
       </c>
       <c r="C27">
-        <v>5.3931452683178692E-2</v>
+        <v>5.3144163194754283E-2</v>
       </c>
       <c r="D27">
-        <v>2.943615467413746E-2</v>
+        <v>3.5438092188961899E-2</v>
       </c>
       <c r="E27">
-        <v>9.8793459992742708E-2</v>
+        <v>9.5743312360310681E-2</v>
       </c>
       <c r="F27">
-        <v>1.7359538918956821E-2</v>
+        <v>2.1778541424050619E-2</v>
       </c>
       <c r="G27">
-        <v>-1.593351392604896E-2</v>
+        <v>-6.3297933090391773E-3</v>
       </c>
       <c r="H27">
-        <v>4.0879453997608527E-2</v>
+        <v>4.9994345132552263E-2</v>
       </c>
       <c r="I27">
-        <v>-3.9735290238990223E-2</v>
+        <v>-2.8063860016616909E-2</v>
       </c>
       <c r="J27">
-        <v>-9.1282508322031053E-2</v>
+        <v>-7.0960304108662109E-2</v>
       </c>
       <c r="K27">
-        <v>-0.1491432755379361</v>
+        <v>-0.1318092827204935</v>
       </c>
       <c r="L27">
-        <v>-0.2467220143520861</v>
+        <v>-0.2191042226044955</v>
       </c>
       <c r="M27">
-        <v>-0.29084430994893462</v>
+        <v>-0.27545801939364872</v>
       </c>
       <c r="N27">
-        <v>-0.1827893331278457</v>
+        <v>-0.17233110161569939</v>
       </c>
       <c r="O27">
-        <v>-0.24580140794724281</v>
+        <v>-0.23797968967426739</v>
       </c>
       <c r="P27">
-        <v>-0.26938299358435591</v>
+        <v>-0.26750937355417331</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
@@ -2017,49 +1920,49 @@
         <v>42</v>
       </c>
       <c r="B28">
-        <v>0.54680047980073476</v>
+        <v>0.54874472947594555</v>
       </c>
       <c r="C28">
-        <v>0.60783129768089172</v>
+        <v>0.61010652457272896</v>
       </c>
       <c r="D28">
-        <v>0.63930795010714569</v>
+        <v>0.64109613918081998</v>
       </c>
       <c r="E28">
-        <v>0.66063924295724641</v>
+        <v>0.66416917803411946</v>
       </c>
       <c r="F28">
-        <v>0.66030180950691619</v>
+        <v>0.66502791721142784</v>
       </c>
       <c r="G28">
-        <v>0.66627452308420387</v>
+        <v>0.66979335342136015</v>
       </c>
       <c r="H28">
-        <v>0.66342098053193466</v>
+        <v>0.66512088602321207</v>
       </c>
       <c r="I28">
-        <v>0.65534355930136101</v>
+        <v>0.65693434795565997</v>
       </c>
       <c r="J28">
-        <v>0.62738605776473089</v>
+        <v>0.63179473387200469</v>
       </c>
       <c r="K28">
-        <v>0.58755273841245048</v>
+        <v>0.5965966648730624</v>
       </c>
       <c r="L28">
-        <v>0.55973810122519341</v>
+        <v>0.56788417082055409</v>
       </c>
       <c r="M28">
-        <v>0.5005133753854405</v>
+        <v>0.51114130827565984</v>
       </c>
       <c r="N28">
-        <v>0.43820243535221892</v>
+        <v>0.44828934462758618</v>
       </c>
       <c r="O28">
-        <v>0.36414857260631128</v>
+        <v>0.37393773763771082</v>
       </c>
       <c r="P28">
-        <v>0.27408556580261062</v>
+        <v>0.28676930676429457</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
@@ -2067,49 +1970,49 @@
         <v>43</v>
       </c>
       <c r="B29">
-        <v>0.54611705982581449</v>
+        <v>0.54265912380465953</v>
       </c>
       <c r="C29">
-        <v>0.6112456656801879</v>
+        <v>0.60928947650734</v>
       </c>
       <c r="D29">
-        <v>0.65469489512158618</v>
+        <v>0.65374506628015683</v>
       </c>
       <c r="E29">
-        <v>0.69120922668625295</v>
+        <v>0.6874624224567264</v>
       </c>
       <c r="F29">
-        <v>0.70480009556297751</v>
+        <v>0.70345282910528439</v>
       </c>
       <c r="G29">
-        <v>0.71455358313462869</v>
+        <v>0.71228016912182501</v>
       </c>
       <c r="H29">
-        <v>0.7082100157322303</v>
+        <v>0.70784868191928563</v>
       </c>
       <c r="I29">
-        <v>0.67919168407874642</v>
+        <v>0.67371123294555069</v>
       </c>
       <c r="J29">
-        <v>0.68049556130922562</v>
+        <v>0.67323552663968933</v>
       </c>
       <c r="K29">
-        <v>0.67799075364207984</v>
+        <v>0.67306111453294004</v>
       </c>
       <c r="L29">
-        <v>0.63723281879748839</v>
+        <v>0.63206682900021471</v>
       </c>
       <c r="M29">
-        <v>0.60843286315676837</v>
+        <v>0.60388276789270756</v>
       </c>
       <c r="N29">
-        <v>0.54920748878676695</v>
+        <v>0.54474296695095759</v>
       </c>
       <c r="O29">
-        <v>0.50755380264082861</v>
+        <v>0.50365401810686306</v>
       </c>
       <c r="P29">
-        <v>0.40464427429125682</v>
+        <v>0.40023640047709302</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
@@ -2117,49 +2020,49 @@
         <v>44</v>
       </c>
       <c r="B30">
-        <v>0.55918788572866551</v>
+        <v>0.55887064876965686</v>
       </c>
       <c r="C30">
-        <v>0.58987994207407157</v>
+        <v>0.59121093775977973</v>
       </c>
       <c r="D30">
-        <v>0.63515949793856508</v>
+        <v>0.6393083188406683</v>
       </c>
       <c r="E30">
-        <v>0.66751027474802027</v>
+        <v>0.67118648670269454</v>
       </c>
       <c r="F30">
-        <v>0.66758706207938656</v>
+        <v>0.67501990234562848</v>
       </c>
       <c r="G30">
-        <v>0.67665890145334029</v>
+        <v>0.68382631929592619</v>
       </c>
       <c r="H30">
-        <v>0.67857196666911135</v>
+        <v>0.68463617630912521</v>
       </c>
       <c r="I30">
-        <v>0.66804402047853961</v>
+        <v>0.67518412187089294</v>
       </c>
       <c r="J30">
-        <v>0.62137872564450181</v>
+        <v>0.63069506516833118</v>
       </c>
       <c r="K30">
-        <v>0.61171290825218294</v>
+        <v>0.62231637992993172</v>
       </c>
       <c r="L30">
-        <v>0.56302839651839176</v>
+        <v>0.56942623418334903</v>
       </c>
       <c r="M30">
-        <v>0.52360820487411186</v>
+        <v>0.53339893189507237</v>
       </c>
       <c r="N30">
-        <v>0.46877539591581591</v>
+        <v>0.47533271457112342</v>
       </c>
       <c r="O30">
-        <v>0.39230237578748228</v>
+        <v>0.39668743343730267</v>
       </c>
       <c r="P30">
-        <v>0.32353754053106287</v>
+        <v>0.33019421741683092</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
@@ -2167,49 +2070,49 @@
         <v>45</v>
       </c>
       <c r="B31">
-        <v>0.56267333764430405</v>
+        <v>0.55943128163829625</v>
       </c>
       <c r="C31">
-        <v>0.59351309471297609</v>
+        <v>0.59207706291993645</v>
       </c>
       <c r="D31">
-        <v>0.64039237755080758</v>
+        <v>0.6396506795246456</v>
       </c>
       <c r="E31">
-        <v>0.67049850048274018</v>
+        <v>0.67083630181021825</v>
       </c>
       <c r="F31">
-        <v>0.67186249613615978</v>
+        <v>0.67219028597998121</v>
       </c>
       <c r="G31">
-        <v>0.679824156500757</v>
+        <v>0.68227049717575783</v>
       </c>
       <c r="H31">
-        <v>0.67948603868130819</v>
+        <v>0.68217278675974768</v>
       </c>
       <c r="I31">
-        <v>0.67017827110309369</v>
+        <v>0.67365057465161682</v>
       </c>
       <c r="J31">
-        <v>0.62802875971260452</v>
+        <v>0.63506442742744562</v>
       </c>
       <c r="K31">
-        <v>0.59680770448642528</v>
+        <v>0.60733608738807321</v>
       </c>
       <c r="L31">
-        <v>0.55049979878886435</v>
+        <v>0.56604301967182835</v>
       </c>
       <c r="M31">
-        <v>0.49970118222201121</v>
+        <v>0.51874461793059046</v>
       </c>
       <c r="N31">
-        <v>0.48175875392076262</v>
+        <v>0.50176225468930225</v>
       </c>
       <c r="O31">
-        <v>0.48588710595228651</v>
+        <v>0.50335681050477132</v>
       </c>
       <c r="P31">
-        <v>0.42837409218317002</v>
+        <v>0.45304122532480889</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
@@ -2217,49 +2120,49 @@
         <v>46</v>
       </c>
       <c r="B32">
-        <v>0.54542904870907338</v>
+        <v>0.54387872840544049</v>
       </c>
       <c r="C32">
-        <v>0.61220159897874593</v>
+        <v>0.61023210834648312</v>
       </c>
       <c r="D32">
-        <v>0.65346146114226611</v>
+        <v>0.65445731123843109</v>
       </c>
       <c r="E32">
-        <v>0.688695224774444</v>
+        <v>0.68934781653930055</v>
       </c>
       <c r="F32">
-        <v>0.70358302325759658</v>
+        <v>0.70284325630841671</v>
       </c>
       <c r="G32">
-        <v>0.71214990410222556</v>
+        <v>0.71192948857146854</v>
       </c>
       <c r="H32">
-        <v>0.70820166985823119</v>
+        <v>0.70587343147855086</v>
       </c>
       <c r="I32">
-        <v>0.67996670595611708</v>
+        <v>0.67697618194455567</v>
       </c>
       <c r="J32">
-        <v>0.67983574730649832</v>
+        <v>0.68010268293746845</v>
       </c>
       <c r="K32">
-        <v>0.67941010122992329</v>
+        <v>0.67979492909689243</v>
       </c>
       <c r="L32">
-        <v>0.65328997020685708</v>
+        <v>0.65314635788802478</v>
       </c>
       <c r="M32">
-        <v>0.60085191108097102</v>
+        <v>0.60283956520067239</v>
       </c>
       <c r="N32">
-        <v>0.58168521754788738</v>
+        <v>0.57951584198915451</v>
       </c>
       <c r="O32">
-        <v>0.56593074842334057</v>
+        <v>0.56365019767617297</v>
       </c>
       <c r="P32">
-        <v>0.52680920009862442</v>
+        <v>0.52478987424956347</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
@@ -2267,49 +2170,49 @@
         <v>47</v>
       </c>
       <c r="B33">
-        <v>0.54164395001875898</v>
+        <v>0.54501096739330379</v>
       </c>
       <c r="C33">
-        <v>0.6079144642152039</v>
+        <v>0.61055067562404497</v>
       </c>
       <c r="D33">
-        <v>0.65159934962977928</v>
+        <v>0.65544515961632765</v>
       </c>
       <c r="E33">
-        <v>0.68758799964375272</v>
+        <v>0.69157594080824014</v>
       </c>
       <c r="F33">
-        <v>0.70373661582557911</v>
+        <v>0.70455476012410245</v>
       </c>
       <c r="G33">
-        <v>0.71177070649818086</v>
+        <v>0.71246890197386958</v>
       </c>
       <c r="H33">
-        <v>0.70655372580939835</v>
+        <v>0.70880947103224168</v>
       </c>
       <c r="I33">
-        <v>0.67599107385162382</v>
+        <v>0.68225056356733738</v>
       </c>
       <c r="J33">
-        <v>0.67685722203394727</v>
+        <v>0.68481075193016439</v>
       </c>
       <c r="K33">
-        <v>0.67527027969175124</v>
+        <v>0.68581297191526525</v>
       </c>
       <c r="L33">
-        <v>0.65064945221654313</v>
+        <v>0.66064029948205705</v>
       </c>
       <c r="M33">
-        <v>0.59894274853479024</v>
+        <v>0.61448612518910828</v>
       </c>
       <c r="N33">
-        <v>0.5706301102574789</v>
+        <v>0.59039312126868515</v>
       </c>
       <c r="O33">
-        <v>0.55236038378912899</v>
+        <v>0.57420762474062959</v>
       </c>
       <c r="P33">
-        <v>0.52144156002375963</v>
+        <v>0.54535165374931083</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
@@ -2317,49 +2220,49 @@
         <v>48</v>
       </c>
       <c r="B34">
-        <v>0.54643626393080447</v>
+        <v>0.54621654326524582</v>
       </c>
       <c r="C34">
-        <v>0.61313884412244402</v>
+        <v>0.61159200367557565</v>
       </c>
       <c r="D34">
-        <v>0.65715387019735483</v>
+        <v>0.65447686060405186</v>
       </c>
       <c r="E34">
-        <v>0.6917113158289353</v>
+        <v>0.69158631195094744</v>
       </c>
       <c r="F34">
-        <v>0.70611077569549496</v>
-      </c>
-      <c r="G34" s="2">
-        <v>0.71533560905811167</v>
+        <v>0.70632007396486629</v>
+      </c>
+      <c r="G34">
+        <v>0.71448837056104531</v>
       </c>
       <c r="H34">
-        <v>0.71183581095923087</v>
+        <v>0.70964570455155418</v>
       </c>
       <c r="I34">
-        <v>0.682284645700727</v>
+        <v>0.68324780886767389</v>
       </c>
       <c r="J34">
-        <v>0.68192221191292657</v>
+        <v>0.68577047213533604</v>
       </c>
       <c r="K34">
-        <v>0.68434024690383166</v>
+        <v>0.68600745894543813</v>
       </c>
       <c r="L34">
-        <v>0.66113663132773592</v>
+        <v>0.66208463118644922</v>
       </c>
       <c r="M34">
-        <v>0.61634840462649276</v>
+        <v>0.62002190094555665</v>
       </c>
       <c r="N34">
-        <v>0.59026795219824635</v>
+        <v>0.59275715781908189</v>
       </c>
       <c r="O34">
-        <v>0.57393483538507528</v>
+        <v>0.5770513990646905</v>
       </c>
       <c r="P34">
-        <v>0.55321945790734794</v>
+        <v>0.55000115474607314</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
@@ -2367,49 +2270,49 @@
         <v>49</v>
       </c>
       <c r="B35">
-        <v>0.54349845601101876</v>
+        <v>0.54239091588430666</v>
       </c>
       <c r="C35">
-        <v>0.61042301854058079</v>
+        <v>0.60880478274559069</v>
       </c>
       <c r="D35">
-        <v>0.65401908870522152</v>
+        <v>0.65344718894792309</v>
       </c>
       <c r="E35">
-        <v>0.69141091509091934</v>
+        <v>0.68966836934389253</v>
       </c>
       <c r="F35">
-        <v>0.7068013798502305</v>
+        <v>0.70474989308254421</v>
       </c>
       <c r="G35">
-        <v>0.71414766141945663</v>
+        <v>0.71505839444691921</v>
       </c>
       <c r="H35">
-        <v>0.71135466215764143</v>
+        <v>0.71064697321848358</v>
       </c>
       <c r="I35">
-        <v>0.6803375071279073</v>
+        <v>0.68279727935286127</v>
       </c>
       <c r="J35">
-        <v>0.68061398028188658</v>
+        <v>0.68564504466566845</v>
       </c>
       <c r="K35">
-        <v>0.68460055696738331</v>
+        <v>0.68718905606238467</v>
       </c>
       <c r="L35">
-        <v>0.66386884348572395</v>
+        <v>0.66473739836359824</v>
       </c>
       <c r="M35">
-        <v>0.62713491913409658</v>
+        <v>0.62382661420327279</v>
       </c>
       <c r="N35">
-        <v>0.59929043524592385</v>
+        <v>0.59587708225460989</v>
       </c>
       <c r="O35">
-        <v>0.58239199425688015</v>
+        <v>0.57653765844575344</v>
       </c>
       <c r="P35">
-        <v>0.57592357037538155</v>
+        <v>0.56985999526077646</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
@@ -2417,49 +2320,49 @@
         <v>50</v>
       </c>
       <c r="B36">
-        <v>0.54361003492410698</v>
+        <v>0.54547571048102328</v>
       </c>
       <c r="C36">
-        <v>0.61064331784032777</v>
+        <v>0.61256593638100154</v>
       </c>
       <c r="D36">
-        <v>0.65524704234747844</v>
+        <v>0.65634642666888243</v>
       </c>
       <c r="E36">
-        <v>0.69053942138486757</v>
+        <v>0.69283865512182818</v>
       </c>
       <c r="F36">
-        <v>0.70447901274946356</v>
+        <v>0.70765231173926624</v>
       </c>
       <c r="G36">
-        <v>0.71303847084389083</v>
+        <v>0.7156547787499643</v>
       </c>
       <c r="H36">
-        <v>0.70759014413303611</v>
+        <v>0.71282709695477497</v>
       </c>
       <c r="I36">
-        <v>0.67794992511939045</v>
+        <v>0.68660497334841619</v>
       </c>
       <c r="J36">
-        <v>0.67985222874278117</v>
+        <v>0.68554052975213575</v>
       </c>
       <c r="K36">
-        <v>0.68086462374403323</v>
+        <v>0.68512947809129399</v>
       </c>
       <c r="L36">
-        <v>0.64347628530682133</v>
+        <v>0.64881304355493818</v>
       </c>
       <c r="M36">
-        <v>0.59883887424462856</v>
+        <v>0.60485122311393302</v>
       </c>
       <c r="N36">
-        <v>0.58111456736482059</v>
+        <v>0.5907212571070376</v>
       </c>
       <c r="O36">
-        <v>0.56755710541215942</v>
+        <v>0.57698565278343528</v>
       </c>
       <c r="P36">
-        <v>0.50467925545745629</v>
+        <v>0.51322892776995499</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
@@ -2467,49 +2370,49 @@
         <v>51</v>
       </c>
       <c r="B37">
-        <v>0.54313284724574851</v>
+        <v>0.54269332642131929</v>
       </c>
       <c r="C37">
-        <v>0.6096375899639277</v>
+        <v>0.60838281836136487</v>
       </c>
       <c r="D37">
-        <v>0.65460915761460492</v>
+        <v>0.65322074985605116</v>
       </c>
       <c r="E37">
-        <v>0.68996946005859849</v>
+        <v>0.69009981178491719</v>
       </c>
       <c r="F37">
-        <v>0.70515298223122491</v>
+        <v>0.70447930165234773</v>
       </c>
       <c r="G37">
-        <v>0.71191546935816308</v>
+        <v>0.71339851352998607</v>
       </c>
       <c r="H37">
-        <v>0.70801849195188404</v>
+        <v>0.70952524473405287</v>
       </c>
       <c r="I37">
-        <v>0.67966509184663193</v>
+        <v>0.68152410877248348</v>
       </c>
       <c r="J37">
-        <v>0.68225069895433399</v>
+        <v>0.68180598411337345</v>
       </c>
       <c r="K37">
-        <v>0.68044458093400306</v>
+        <v>0.68165499058289691</v>
       </c>
       <c r="L37">
-        <v>0.64554249897252314</v>
+        <v>0.6468403664603356</v>
       </c>
       <c r="M37">
-        <v>0.59596992991472786</v>
+        <v>0.59714769981717963</v>
       </c>
       <c r="N37">
-        <v>0.57618961719398132</v>
+        <v>0.57888182297721191</v>
       </c>
       <c r="O37">
-        <v>0.56196315251218387</v>
+        <v>0.56602043865433149</v>
       </c>
       <c r="P37">
-        <v>0.50756136363403281</v>
+        <v>0.50859252096424024</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
@@ -2517,49 +2420,49 @@
         <v>52</v>
       </c>
       <c r="B38">
-        <v>0.54454803103492588</v>
+        <v>0.54409028112192726</v>
       </c>
       <c r="C38">
-        <v>0.61043802354730747</v>
+        <v>0.60959198609684195</v>
       </c>
       <c r="D38">
-        <v>0.65352350897067013</v>
+        <v>0.65129235583034961</v>
       </c>
       <c r="E38">
-        <v>0.6898381836751124</v>
+        <v>0.68856842732739154</v>
       </c>
       <c r="F38">
-        <v>0.70451765056224624</v>
+        <v>0.70413557860343057</v>
       </c>
       <c r="G38">
-        <v>0.71308791134068317</v>
+        <v>0.71136254350926198</v>
       </c>
       <c r="H38">
-        <v>0.70821974891873007</v>
+        <v>0.70439696628321091</v>
       </c>
       <c r="I38">
-        <v>0.67796394268259896</v>
+        <v>0.67655655385733027</v>
       </c>
       <c r="J38">
-        <v>0.68150193076034415</v>
+        <v>0.67992700039439458</v>
       </c>
       <c r="K38">
-        <v>0.68117494858648864</v>
+        <v>0.67884884003457679</v>
       </c>
       <c r="L38">
-        <v>0.64688638815280031</v>
+        <v>0.64819360301445428</v>
       </c>
       <c r="M38">
-        <v>0.59369985364753786</v>
+        <v>0.59597083611695179</v>
       </c>
       <c r="N38">
-        <v>0.57249003631933415</v>
+        <v>0.57479613300480958</v>
       </c>
       <c r="O38">
-        <v>0.55892381494551868</v>
+        <v>0.56104501900262227</v>
       </c>
       <c r="P38">
-        <v>0.51523316627525384</v>
+        <v>0.5143294709288625</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
@@ -2567,49 +2470,49 @@
         <v>53</v>
       </c>
       <c r="B39">
-        <v>0.54280254520039695</v>
+        <v>0.54248380046046296</v>
       </c>
       <c r="C39">
-        <v>0.60903795859364429</v>
+        <v>0.60865896444448431</v>
       </c>
       <c r="D39">
-        <v>0.65292692113757778</v>
+        <v>0.65191879761657634</v>
       </c>
       <c r="E39">
-        <v>0.68950340097543772</v>
+        <v>0.68884458802753912</v>
       </c>
       <c r="F39">
-        <v>0.70394572022257018</v>
+        <v>0.70421998266499086</v>
       </c>
       <c r="G39">
-        <v>0.71239667809910734</v>
+        <v>0.71231037097319605</v>
       </c>
       <c r="H39">
-        <v>0.70872674880596775</v>
+        <v>0.70819749127530807</v>
       </c>
       <c r="I39">
-        <v>0.67920395435784719</v>
+        <v>0.68202200453149775</v>
       </c>
       <c r="J39">
-        <v>0.68147381252189687</v>
+        <v>0.68366062472814881</v>
       </c>
       <c r="K39">
-        <v>0.67781732438988318</v>
+        <v>0.68409148565495925</v>
       </c>
       <c r="L39">
-        <v>0.64788198466255831</v>
+        <v>0.6501878530751376</v>
       </c>
       <c r="M39">
-        <v>0.59413802460258269</v>
+        <v>0.59884635283724419</v>
       </c>
       <c r="N39">
-        <v>0.5712298133990954</v>
+        <v>0.5739631022635453</v>
       </c>
       <c r="O39">
-        <v>0.56176993143149712</v>
+        <v>0.56087595338000207</v>
       </c>
       <c r="P39">
-        <v>0.52613028913359494</v>
+        <v>0.51366305746007546</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
@@ -2617,49 +2520,49 @@
         <v>54</v>
       </c>
       <c r="B40">
-        <v>0.54075997671054687</v>
+        <v>0.5443221077111654</v>
       </c>
       <c r="C40">
-        <v>0.60816570291664174</v>
+        <v>0.61140334239458516</v>
       </c>
       <c r="D40">
-        <v>0.65179374069397911</v>
+        <v>0.65503533781672896</v>
       </c>
       <c r="E40">
-        <v>0.688461801360846</v>
+        <v>0.69080640735778787</v>
       </c>
       <c r="F40">
-        <v>0.70529888898367787</v>
+        <v>0.70398305847749787</v>
       </c>
       <c r="G40">
-        <v>0.71259060975434563</v>
+        <v>0.71519526065583727</v>
       </c>
       <c r="H40">
-        <v>0.71010922881464067</v>
+        <v>0.71012906132938036</v>
       </c>
       <c r="I40">
-        <v>0.68055000270351229</v>
+        <v>0.68255288746672038</v>
       </c>
       <c r="J40">
-        <v>0.68254249134469269</v>
+        <v>0.68322075599994991</v>
       </c>
       <c r="K40">
-        <v>0.6843945186342868</v>
+        <v>0.68608676331404272</v>
       </c>
       <c r="L40">
-        <v>0.66108051288432512</v>
+        <v>0.66446647354910038</v>
       </c>
       <c r="M40">
-        <v>0.62157659004937327</v>
+        <v>0.62452666400935231</v>
       </c>
       <c r="N40">
-        <v>0.59413588534478401</v>
+        <v>0.59621584748028345</v>
       </c>
       <c r="O40">
-        <v>0.57701662933631837</v>
+        <v>0.58021243447879534</v>
       </c>
       <c r="P40">
-        <v>0.56172431189606997</v>
+        <v>0.56598385457978428</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
@@ -2667,49 +2570,49 @@
         <v>55</v>
       </c>
       <c r="B41">
-        <v>0.5545945741040853</v>
+        <v>0.55554700448183414</v>
       </c>
       <c r="C41">
-        <v>0.59912259880078678</v>
+        <v>0.59481214257864679</v>
       </c>
       <c r="D41">
-        <v>0.66388449219587076</v>
+        <v>0.66283114628119744</v>
       </c>
       <c r="E41">
-        <v>0.67515682515220576</v>
+        <v>0.67439103484802509</v>
       </c>
       <c r="F41">
-        <v>0.63225413287871113</v>
+        <v>0.6321488464735141</v>
       </c>
       <c r="G41">
-        <v>0.62081688245317834</v>
+        <v>0.62117728255586557</v>
       </c>
       <c r="H41">
-        <v>0.63485444795421331</v>
+        <v>0.63727156599137691</v>
       </c>
       <c r="I41">
-        <v>0.61352201074851076</v>
+        <v>0.61711548223974444</v>
       </c>
       <c r="J41">
-        <v>0.55969228000163285</v>
+        <v>0.56339630056822709</v>
       </c>
       <c r="K41">
-        <v>0.51414943337652808</v>
+        <v>0.51559618283687592</v>
       </c>
       <c r="L41">
-        <v>0.47291437970248262</v>
+        <v>0.47743052580978029</v>
       </c>
       <c r="M41">
-        <v>0.43403618087654788</v>
+        <v>0.44114145874954441</v>
       </c>
       <c r="N41">
-        <v>0.40854034250779581</v>
+        <v>0.41710808837806368</v>
       </c>
       <c r="O41">
-        <v>0.37513632965914218</v>
+        <v>0.38415373024155008</v>
       </c>
       <c r="P41">
-        <v>0.35036092979003902</v>
+        <v>0.36340303575451721</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
@@ -2717,49 +2620,49 @@
         <v>56</v>
       </c>
       <c r="B42">
-        <v>0.55743116127855918</v>
+        <v>0.55623775860621838</v>
       </c>
       <c r="C42">
-        <v>0.61234236185193724</v>
+        <v>0.60765749031287197</v>
       </c>
       <c r="D42">
-        <v>0.67406064965157797</v>
+        <v>0.67097725271183628</v>
       </c>
       <c r="E42">
-        <v>0.67860530257926854</v>
+        <v>0.67511229887781765</v>
       </c>
       <c r="F42">
-        <v>0.65258706159848734</v>
+        <v>0.64559174380674733</v>
       </c>
       <c r="G42">
-        <v>0.6290728379845627</v>
+        <v>0.62375108416750824</v>
       </c>
       <c r="H42">
-        <v>0.66586596027524614</v>
+        <v>0.66304751309166288</v>
       </c>
       <c r="I42">
-        <v>0.640769083474648</v>
+        <v>0.6403896975032598</v>
       </c>
       <c r="J42">
-        <v>0.60000745227992969</v>
+        <v>0.60323832718003412</v>
       </c>
       <c r="K42">
-        <v>0.57430836848309852</v>
+        <v>0.5776440363941403</v>
       </c>
       <c r="L42">
-        <v>0.55768223438114661</v>
+        <v>0.56010305714433428</v>
       </c>
       <c r="M42">
-        <v>0.51577120477223426</v>
+        <v>0.51894437191841591</v>
       </c>
       <c r="N42">
-        <v>0.47315341641686359</v>
+        <v>0.47369564536547998</v>
       </c>
       <c r="O42">
-        <v>0.41715403456223249</v>
+        <v>0.42160014521246469</v>
       </c>
       <c r="P42">
-        <v>0.36697022247787409</v>
+        <v>0.36741003192566107</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
@@ -2767,49 +2670,49 @@
         <v>57</v>
       </c>
       <c r="B43">
-        <v>0.55846049582136814</v>
+        <v>0.55810161213117238</v>
       </c>
       <c r="C43">
-        <v>0.6117184352120737</v>
+        <v>0.6107026454905462</v>
       </c>
       <c r="D43">
-        <v>0.67537340992976391</v>
+        <v>0.6704596401654459</v>
       </c>
       <c r="E43">
-        <v>0.67945462955964842</v>
+        <v>0.67561299874990344</v>
       </c>
       <c r="F43">
-        <v>0.66159915278817083</v>
+        <v>0.65875598012798176</v>
       </c>
       <c r="G43">
-        <v>0.64359247860597923</v>
+        <v>0.63564157291004819</v>
       </c>
       <c r="H43">
-        <v>0.66416331587278898</v>
+        <v>0.65658519210493727</v>
       </c>
       <c r="I43">
-        <v>0.63766856052083176</v>
+        <v>0.629512014185442</v>
       </c>
       <c r="J43">
-        <v>0.59839005190236083</v>
+        <v>0.58978347388776142</v>
       </c>
       <c r="K43">
-        <v>0.55429546450671008</v>
+        <v>0.54614372427450331</v>
       </c>
       <c r="L43">
-        <v>0.52091123008624329</v>
+        <v>0.51420538164904994</v>
       </c>
       <c r="M43">
-        <v>0.46653389876487628</v>
+        <v>0.45488149811272149</v>
       </c>
       <c r="N43">
-        <v>0.4408383010150102</v>
+        <v>0.430847553442056</v>
       </c>
       <c r="O43">
-        <v>0.42693820467205701</v>
+        <v>0.42039256455549689</v>
       </c>
       <c r="P43">
-        <v>0.39459700367922018</v>
+        <v>0.38224542246214382</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
@@ -2817,49 +2720,49 @@
         <v>58</v>
       </c>
       <c r="B44">
-        <v>0.51235655570019689</v>
+        <v>0.51428358574879629</v>
       </c>
       <c r="C44">
-        <v>0.51808103511882442</v>
+        <v>0.51618540672577273</v>
       </c>
       <c r="D44">
-        <v>0.55100276118453373</v>
+        <v>0.54583290357820724</v>
       </c>
       <c r="E44">
-        <v>0.58076930929786452</v>
+        <v>0.58115726672932488</v>
       </c>
       <c r="F44">
-        <v>0.61572459198801066</v>
+        <v>0.62112993159373997</v>
       </c>
       <c r="G44">
-        <v>0.61296787935963148</v>
+        <v>0.61983200298450747</v>
       </c>
       <c r="H44">
-        <v>0.57019374195494821</v>
+        <v>0.57838328618130419</v>
       </c>
       <c r="I44">
-        <v>0.55194408713189103</v>
+        <v>0.55953064842307587</v>
       </c>
       <c r="J44">
-        <v>0.52379434913404532</v>
+        <v>0.53115763320923615</v>
       </c>
       <c r="K44">
-        <v>0.47633375924355298</v>
+        <v>0.48209616101695862</v>
       </c>
       <c r="L44">
-        <v>0.40154771233243708</v>
+        <v>0.41067168872402599</v>
       </c>
       <c r="M44">
-        <v>0.32052702556006468</v>
+        <v>0.3280004192871166</v>
       </c>
       <c r="N44">
-        <v>0.26692114857776811</v>
+        <v>0.26954951593613591</v>
       </c>
       <c r="O44">
-        <v>0.2018272430857217</v>
+        <v>0.19863451271935609</v>
       </c>
       <c r="P44">
-        <v>0.13646626483452109</v>
+        <v>0.12876007633470299</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
@@ -2867,49 +2770,49 @@
         <v>59</v>
       </c>
       <c r="B45">
-        <v>0.49055355573596088</v>
+        <v>0.49192811968451672</v>
       </c>
       <c r="C45">
-        <v>0.51884610392495001</v>
+        <v>0.52036995908459371</v>
       </c>
       <c r="D45">
-        <v>0.47238092737559351</v>
+        <v>0.47418228992367017</v>
       </c>
       <c r="E45">
-        <v>0.4125641103283369</v>
+        <v>0.41718958566283249</v>
       </c>
       <c r="F45">
-        <v>0.3489306687745255</v>
+        <v>0.35950047213996761</v>
       </c>
       <c r="G45">
-        <v>0.35419437691538519</v>
+        <v>0.36310108064170021</v>
       </c>
       <c r="H45">
-        <v>0.38734094346180298</v>
+        <v>0.39538261903251037</v>
       </c>
       <c r="I45">
-        <v>0.40238360086006159</v>
+        <v>0.40503563086244632</v>
       </c>
       <c r="J45">
-        <v>0.40158810410322843</v>
+        <v>0.40592730050035281</v>
       </c>
       <c r="K45">
-        <v>0.34141072194202549</v>
+        <v>0.34795238428333269</v>
       </c>
       <c r="L45">
-        <v>0.25210526551421902</v>
+        <v>0.25963465335725611</v>
       </c>
       <c r="M45">
-        <v>0.2061155354112077</v>
+        <v>0.2089824202674577</v>
       </c>
       <c r="N45">
-        <v>0.1732160306393718</v>
+        <v>0.17542031568913119</v>
       </c>
       <c r="O45">
-        <v>0.12712967003519199</v>
+        <v>0.12934878607467601</v>
       </c>
       <c r="P45">
-        <v>0.11837648965769521</v>
+        <v>0.12676617247618421</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
@@ -2917,49 +2820,49 @@
         <v>60</v>
       </c>
       <c r="B46">
-        <v>0.4466464057135463</v>
+        <v>0.44928299014085732</v>
       </c>
       <c r="C46">
-        <v>0.51506950485291392</v>
+        <v>0.51541424991370854</v>
       </c>
       <c r="D46">
-        <v>0.49392167802978248</v>
+        <v>0.49235370973684861</v>
       </c>
       <c r="E46">
-        <v>0.50291229789928371</v>
+        <v>0.50007881953944422</v>
       </c>
       <c r="F46">
-        <v>0.49462311245883939</v>
+        <v>0.4978490957571986</v>
       </c>
       <c r="G46">
-        <v>0.51298080579499228</v>
+        <v>0.51379730811424384</v>
       </c>
       <c r="H46">
-        <v>0.52950108758655978</v>
+        <v>0.53341329675453641</v>
       </c>
       <c r="I46">
-        <v>0.48362019891129648</v>
+        <v>0.48948918185050039</v>
       </c>
       <c r="J46">
-        <v>0.43942679838401583</v>
+        <v>0.44898669822205201</v>
       </c>
       <c r="K46">
-        <v>0.37735787465473009</v>
+        <v>0.38771819997458118</v>
       </c>
       <c r="L46">
-        <v>0.35638725110613062</v>
+        <v>0.36737363208909429</v>
       </c>
       <c r="M46">
-        <v>0.34354791315970068</v>
+        <v>0.35959577604576282</v>
       </c>
       <c r="N46">
-        <v>0.31988345939235241</v>
+        <v>0.33854719003512801</v>
       </c>
       <c r="O46">
-        <v>0.29641964504230622</v>
+        <v>0.31317092226850129</v>
       </c>
       <c r="P46">
-        <v>0.2651539477926147</v>
+        <v>0.28861375297635372</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
@@ -2967,54 +2870,54 @@
         <v>61</v>
       </c>
       <c r="B47">
-        <v>0.51897304694117508</v>
+        <v>0.51939035798141875</v>
       </c>
       <c r="C47">
-        <v>0.49311073338676242</v>
+        <v>0.49338147706636332</v>
       </c>
       <c r="D47">
-        <v>0.47780222890035978</v>
+        <v>0.47846062741960532</v>
       </c>
       <c r="E47">
-        <v>0.44711817705501627</v>
+        <v>0.44529359144546882</v>
       </c>
       <c r="F47">
-        <v>0.39717505772830342</v>
+        <v>0.38997874881295519</v>
       </c>
       <c r="G47">
-        <v>0.40508109875983611</v>
+        <v>0.40160264539317031</v>
       </c>
       <c r="H47">
-        <v>0.49263510858041981</v>
+        <v>0.48942988580145907</v>
       </c>
       <c r="I47">
-        <v>0.5148280851889343</v>
+        <v>0.50919972283923509</v>
       </c>
       <c r="J47">
-        <v>0.49264760564480498</v>
+        <v>0.48214184288000878</v>
       </c>
       <c r="K47">
-        <v>0.43191466762988029</v>
+        <v>0.41740294287425289</v>
       </c>
       <c r="L47">
-        <v>0.40545867936613628</v>
+        <v>0.3965590717395841</v>
       </c>
       <c r="M47">
-        <v>0.38941328993856761</v>
+        <v>0.38034468840500479</v>
       </c>
       <c r="N47">
-        <v>0.37853501837298581</v>
+        <v>0.37470670799762662</v>
       </c>
       <c r="O47">
-        <v>0.38156461613373499</v>
+        <v>0.37954548219555517</v>
       </c>
       <c r="P47">
-        <v>0.3791756085359293</v>
+        <v>0.37835247630222019</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P33 B35:P47 B34:F34 H34:P34">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="B2:P47">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3024,8 +2927,6 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="top10" dxfId="2" priority="2" rank="10"/>
-    <cfRule type="top10" dxfId="3" priority="1" rank="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ROSA_vitaSPEC/Results/test_pretraitements/trans.beta.carotenes/Resultats_trans.beta.carotenes_moy_ADJR2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/trans.beta.carotenes/Resultats_trans.beta.carotenes_moy_ADJR2.xlsx
@@ -1,217 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\trans.beta.carotenes\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>LV1_ADJR2</t>
-  </si>
-  <si>
-    <t>LV2_ADJR2</t>
-  </si>
-  <si>
-    <t>LV3_ADJR2</t>
-  </si>
-  <si>
-    <t>LV4_ADJR2</t>
-  </si>
-  <si>
-    <t>LV5_ADJR2</t>
-  </si>
-  <si>
-    <t>LV6_ADJR2</t>
-  </si>
-  <si>
-    <t>LV7_ADJR2</t>
-  </si>
-  <si>
-    <t>LV8_ADJR2</t>
-  </si>
-  <si>
-    <t>LV9_ADJR2</t>
-  </si>
-  <si>
-    <t>LV10_ADJR2</t>
-  </si>
-  <si>
-    <t>LV11_ADJR2</t>
-  </si>
-  <si>
-    <t>LV12_ADJR2</t>
-  </si>
-  <si>
-    <t>LV13_ADJR2</t>
-  </si>
-  <si>
-    <t>LV14_ADJR2</t>
-  </si>
-  <si>
-    <t>LV15_ADJR2</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -259,19 +63,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -313,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -345,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -380,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -556,2378 +350,2408 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="16" width="12.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q43"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>16</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>LV0_ADJR2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_ADJR2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_ADJR2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_ADJR2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_ADJR2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_ADJR2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_ADJR2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_ADJR2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_ADJR2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_ADJR2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_ADJR2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_ADJR2</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_ADJR2</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_ADJR2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_ADJR2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_ADJR2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>0.33600596974602331</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C2">
-        <v>0.48215333580767539</v>
+        <v>0.3353062153870255</v>
       </c>
       <c r="D2">
-        <v>0.50538712527943852</v>
+        <v>0.4823595084705218</v>
       </c>
       <c r="E2">
-        <v>0.53098784773864838</v>
+        <v>0.5081955861761949</v>
       </c>
       <c r="F2">
-        <v>0.51809585601972741</v>
+        <v>0.5333802489015617</v>
       </c>
       <c r="G2">
-        <v>0.53363408493219355</v>
+        <v>0.5216838862245874</v>
       </c>
       <c r="H2">
-        <v>0.5277387494100948</v>
+        <v>0.5352403431064203</v>
       </c>
       <c r="I2">
-        <v>0.52592910243753854</v>
+        <v>0.5282598999751407</v>
       </c>
       <c r="J2">
-        <v>0.52890108971948846</v>
+        <v>0.5296732575848453</v>
       </c>
       <c r="K2">
-        <v>0.52562039990743559</v>
+        <v>0.5335151123882722</v>
       </c>
       <c r="L2">
-        <v>0.48934039420253272</v>
+        <v>0.5279716625312988</v>
       </c>
       <c r="M2">
-        <v>0.45104360788558778</v>
+        <v>0.486403215276047</v>
       </c>
       <c r="N2">
-        <v>0.4191487725345005</v>
+        <v>0.4445236923096994</v>
       </c>
       <c r="O2">
-        <v>0.37039663785206067</v>
+        <v>0.4059247962310366</v>
       </c>
       <c r="P2">
-        <v>0.40441243121599008</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>17</v>
+        <v>0.3498435429521971</v>
+      </c>
+      <c r="Q2">
+        <v>0.3844833611124653</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>0.43643307274762527</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C3">
-        <v>0.49710430618553808</v>
+        <v>0.4356561364082591</v>
       </c>
       <c r="D3">
-        <v>0.49314014236650328</v>
+        <v>0.4950220704442346</v>
       </c>
       <c r="E3">
-        <v>0.50305764492731941</v>
+        <v>0.4899940110678813</v>
       </c>
       <c r="F3">
-        <v>0.50395960905542958</v>
+        <v>0.4972298731757591</v>
       </c>
       <c r="G3">
-        <v>0.51385482468392651</v>
+        <v>0.4906856152266162</v>
       </c>
       <c r="H3">
-        <v>0.48065623280606301</v>
+        <v>0.4991610792246614</v>
       </c>
       <c r="I3">
-        <v>0.46852431402543793</v>
+        <v>0.4608519904117899</v>
       </c>
       <c r="J3">
-        <v>0.45159382875109799</v>
+        <v>0.4521018339834321</v>
       </c>
       <c r="K3">
-        <v>0.43315180553543547</v>
+        <v>0.4348188461993894</v>
       </c>
       <c r="L3">
-        <v>0.39700224947554857</v>
+        <v>0.4221307471930163</v>
       </c>
       <c r="M3">
-        <v>0.31824143819712031</v>
+        <v>0.3840564001701857</v>
       </c>
       <c r="N3">
-        <v>0.2326443521762368</v>
+        <v>0.2984207527796077</v>
       </c>
       <c r="O3">
-        <v>0.179548282138319</v>
+        <v>0.2171936149912482</v>
       </c>
       <c r="P3">
-        <v>0.11767619753732091</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
+        <v>0.1665514006362288</v>
+      </c>
+      <c r="Q3">
+        <v>0.1136461733308757</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>0.35762896617122047</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C4">
-        <v>0.47565325435307498</v>
+        <v>0.3532185754510117</v>
       </c>
       <c r="D4">
-        <v>0.48835775097321232</v>
+        <v>0.4711914914257969</v>
       </c>
       <c r="E4">
-        <v>0.48462497113940761</v>
+        <v>0.482912798209363</v>
       </c>
       <c r="F4">
-        <v>0.5143558208348169</v>
+        <v>0.4776921679467109</v>
       </c>
       <c r="G4">
-        <v>0.55630038713721197</v>
+        <v>0.509371881241155</v>
       </c>
       <c r="H4">
-        <v>0.57078544667301712</v>
+        <v>0.548585700956611</v>
       </c>
       <c r="I4">
-        <v>0.53601508258965658</v>
+        <v>0.5650905644693086</v>
       </c>
       <c r="J4">
-        <v>0.49122019440838199</v>
+        <v>0.5296641360936188</v>
       </c>
       <c r="K4">
-        <v>0.45911302894855449</v>
+        <v>0.4857163916632518</v>
       </c>
       <c r="L4">
-        <v>0.37941888038126248</v>
+        <v>0.4569269148814896</v>
       </c>
       <c r="M4">
-        <v>0.38776828167488481</v>
+        <v>0.3715103200380634</v>
       </c>
       <c r="N4">
-        <v>0.42689327147882211</v>
+        <v>0.3791872173943013</v>
       </c>
       <c r="O4">
-        <v>0.45277679518993352</v>
+        <v>0.4185372121811104</v>
       </c>
       <c r="P4">
-        <v>0.45571125944701019</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
+        <v>0.4439244751413325</v>
+      </c>
+      <c r="Q4">
+        <v>0.4497581308572946</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>0.48815911964664999</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C5">
-        <v>0.49315046738336082</v>
+        <v>0.4874979076603262</v>
       </c>
       <c r="D5">
-        <v>0.49956090371780271</v>
+        <v>0.4916419037445325</v>
       </c>
       <c r="E5">
-        <v>0.5231374757453594</v>
+        <v>0.4979383097359529</v>
       </c>
       <c r="F5">
-        <v>0.51755068374100199</v>
+        <v>0.516434200953085</v>
       </c>
       <c r="G5">
-        <v>0.52356338476102615</v>
+        <v>0.508722295448809</v>
       </c>
       <c r="H5">
-        <v>0.5215421262895007</v>
+        <v>0.51646986117423</v>
       </c>
       <c r="I5">
-        <v>0.48965290518510313</v>
+        <v>0.5176618056860134</v>
       </c>
       <c r="J5">
-        <v>0.45634274227976918</v>
+        <v>0.483171947349438</v>
       </c>
       <c r="K5">
-        <v>0.416936751507194</v>
+        <v>0.4525275195593944</v>
       </c>
       <c r="L5">
-        <v>0.38110828131084512</v>
+        <v>0.4078485123356302</v>
       </c>
       <c r="M5">
-        <v>0.36617289409415571</v>
+        <v>0.3700754718951436</v>
       </c>
       <c r="N5">
-        <v>0.39512190423081178</v>
+        <v>0.3628047769761227</v>
       </c>
       <c r="O5">
-        <v>0.40153174573112388</v>
+        <v>0.3928311887113297</v>
       </c>
       <c r="P5">
-        <v>0.42338442594178688</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>20</v>
+        <v>0.4074289294568985</v>
+      </c>
+      <c r="Q5">
+        <v>0.4256990645495322</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>0.49165493334850358</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C6">
-        <v>0.49582398781431292</v>
+        <v>0.4893478964610107</v>
       </c>
       <c r="D6">
-        <v>0.50156272993811968</v>
+        <v>0.4914685308011539</v>
       </c>
       <c r="E6">
-        <v>0.51137873657114608</v>
+        <v>0.4977745562831248</v>
       </c>
       <c r="F6">
-        <v>0.54052224963128437</v>
+        <v>0.5109351767467419</v>
       </c>
       <c r="G6">
-        <v>0.5252368291509526</v>
+        <v>0.544417034476058</v>
       </c>
       <c r="H6">
-        <v>0.51691463362043111</v>
+        <v>0.5277847076255636</v>
       </c>
       <c r="I6">
-        <v>0.46945158699888129</v>
+        <v>0.5205530726702803</v>
       </c>
       <c r="J6">
-        <v>0.42395920841492313</v>
+        <v>0.472860757709676</v>
       </c>
       <c r="K6">
-        <v>0.39778426425289809</v>
+        <v>0.4267825119677324</v>
       </c>
       <c r="L6">
-        <v>0.3642497142788651</v>
+        <v>0.4057787000364377</v>
       </c>
       <c r="M6">
-        <v>0.36291833799662709</v>
+        <v>0.3675058653907685</v>
       </c>
       <c r="N6">
-        <v>0.34666652289401051</v>
+        <v>0.3681164566464987</v>
       </c>
       <c r="O6">
-        <v>0.36732427747739149</v>
+        <v>0.3518586361536187</v>
       </c>
       <c r="P6">
-        <v>0.37772087141620603</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>21</v>
+        <v>0.3786998255278396</v>
+      </c>
+      <c r="Q6">
+        <v>0.3843031669393525</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>0.35285322087333187</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C7">
-        <v>0.48488361063472851</v>
+        <v>0.3513330846687935</v>
       </c>
       <c r="D7">
-        <v>0.5424661021081103</v>
+        <v>0.4841112200999967</v>
       </c>
       <c r="E7">
-        <v>0.57790225645532001</v>
+        <v>0.5416513783062097</v>
       </c>
       <c r="F7">
-        <v>0.58398132044460038</v>
+        <v>0.5781307879013251</v>
       </c>
       <c r="G7">
-        <v>0.58294463166668453</v>
+        <v>0.5816359439723365</v>
       </c>
       <c r="H7">
-        <v>0.57361971397751632</v>
+        <v>0.5790105046790228</v>
       </c>
       <c r="I7">
-        <v>0.577406567778871</v>
+        <v>0.567109255942938</v>
       </c>
       <c r="J7">
-        <v>0.54388166033043805</v>
+        <v>0.5698662345822213</v>
       </c>
       <c r="K7">
-        <v>0.50202072942855991</v>
+        <v>0.5364917322150535</v>
       </c>
       <c r="L7">
-        <v>0.47633201942183179</v>
+        <v>0.4867715954873714</v>
       </c>
       <c r="M7">
-        <v>0.43753350105739902</v>
+        <v>0.4596866766507122</v>
       </c>
       <c r="N7">
-        <v>0.43708029813230481</v>
+        <v>0.4212333182789867</v>
       </c>
       <c r="O7">
-        <v>0.46055909892464669</v>
+        <v>0.4221630155177387</v>
       </c>
       <c r="P7">
-        <v>0.47856457611317482</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>22</v>
+        <v>0.4485982223166355</v>
+      </c>
+      <c r="Q7">
+        <v>0.4643276050002896</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>0.4001474805298928</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C8">
-        <v>0.46572511602997102</v>
+        <v>0.4048592238485923</v>
       </c>
       <c r="D8">
-        <v>0.51890113435071505</v>
+        <v>0.4689078541950666</v>
       </c>
       <c r="E8">
-        <v>0.52675271155904047</v>
+        <v>0.5215021568587987</v>
       </c>
       <c r="F8">
-        <v>0.53041777114567634</v>
+        <v>0.5287944436882419</v>
       </c>
       <c r="G8">
-        <v>0.52992277955474998</v>
+        <v>0.5315541842065709</v>
       </c>
       <c r="H8">
-        <v>0.54228544919168775</v>
+        <v>0.5275831476242114</v>
       </c>
       <c r="I8">
-        <v>0.52396689574732669</v>
+        <v>0.5371184301697859</v>
       </c>
       <c r="J8">
-        <v>0.49117868007983773</v>
+        <v>0.5200495651757495</v>
       </c>
       <c r="K8">
-        <v>0.43273720032675772</v>
+        <v>0.4857393043573455</v>
       </c>
       <c r="L8">
-        <v>0.38239897177012599</v>
+        <v>0.4268767320692729</v>
       </c>
       <c r="M8">
-        <v>0.38317543229012102</v>
+        <v>0.3763330057821055</v>
       </c>
       <c r="N8">
-        <v>0.41521346830214079</v>
+        <v>0.380475247307285</v>
       </c>
       <c r="O8">
-        <v>0.44240189446850842</v>
+        <v>0.4188491532596547</v>
       </c>
       <c r="P8">
-        <v>0.4242527875675462</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>23</v>
+        <v>0.446589728180221</v>
+      </c>
+      <c r="Q8">
+        <v>0.4291950814301214</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>0.40466270587506592</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C9">
-        <v>0.47039360496984578</v>
+        <v>0.3992843833135249</v>
       </c>
       <c r="D9">
-        <v>0.5233909198492166</v>
+        <v>0.4632396808401539</v>
       </c>
       <c r="E9">
-        <v>0.5294246398178053</v>
+        <v>0.5165362001088351</v>
       </c>
       <c r="F9">
-        <v>0.53130741491307154</v>
+        <v>0.5234015328082022</v>
       </c>
       <c r="G9">
-        <v>0.5260768164709263</v>
+        <v>0.5262048721872374</v>
       </c>
       <c r="H9">
-        <v>0.53988403822109421</v>
+        <v>0.5224928617725974</v>
       </c>
       <c r="I9">
-        <v>0.52410539825282954</v>
+        <v>0.5355290400504965</v>
       </c>
       <c r="J9">
-        <v>0.50896938202655406</v>
+        <v>0.5231425580878106</v>
       </c>
       <c r="K9">
-        <v>0.47579084800895421</v>
+        <v>0.5039180383336583</v>
       </c>
       <c r="L9">
-        <v>0.42841038809694232</v>
+        <v>0.4702630112524578</v>
       </c>
       <c r="M9">
-        <v>0.42777514958518881</v>
+        <v>0.4183211330652407</v>
       </c>
       <c r="N9">
-        <v>0.46301590204549509</v>
+        <v>0.4176832794107133</v>
       </c>
       <c r="O9">
-        <v>0.49383939707327063</v>
+        <v>0.4538651696237254</v>
       </c>
       <c r="P9">
-        <v>0.47421022215591069</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>24</v>
+        <v>0.485300046100218</v>
+      </c>
+      <c r="Q9">
+        <v>0.459108184936</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>0.39926159444176612</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C10">
-        <v>0.46037356633938992</v>
+        <v>0.4033305299588883</v>
       </c>
       <c r="D10">
-        <v>0.51461924672822679</v>
+        <v>0.4682542415506873</v>
       </c>
       <c r="E10">
-        <v>0.51853270570402665</v>
+        <v>0.5242787098616065</v>
       </c>
       <c r="F10">
-        <v>0.52040123289649332</v>
+        <v>0.5296614262145308</v>
       </c>
       <c r="G10">
-        <v>0.51696176367577618</v>
+        <v>0.5320677773099903</v>
       </c>
       <c r="H10">
-        <v>0.53216000814848063</v>
+        <v>0.5288608126344355</v>
       </c>
       <c r="I10">
-        <v>0.51923743736160821</v>
+        <v>0.5417197850971592</v>
       </c>
       <c r="J10">
-        <v>0.50207598675056408</v>
+        <v>0.5314236816607815</v>
       </c>
       <c r="K10">
-        <v>0.47423267401986058</v>
+        <v>0.5130457453485734</v>
       </c>
       <c r="L10">
-        <v>0.42679159498852381</v>
+        <v>0.4819869051400479</v>
       </c>
       <c r="M10">
-        <v>0.42502154064543912</v>
+        <v>0.4278194143939073</v>
       </c>
       <c r="N10">
-        <v>0.45605455015724528</v>
+        <v>0.4277471787957555</v>
       </c>
       <c r="O10">
-        <v>0.4903762124327522</v>
+        <v>0.4637506540024175</v>
       </c>
       <c r="P10">
-        <v>0.47096688949766929</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>25</v>
+        <v>0.4967461084166058</v>
+      </c>
+      <c r="Q10">
+        <v>0.4736298384676954</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>0.40651154959852892</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C11">
-        <v>0.47229019369322528</v>
+        <v>0.4039901037878459</v>
       </c>
       <c r="D11">
-        <v>0.52524740911081647</v>
+        <v>0.4685855093761084</v>
       </c>
       <c r="E11">
-        <v>0.53277923459912979</v>
+        <v>0.5177653481720358</v>
       </c>
       <c r="F11">
-        <v>0.53479804354606031</v>
+        <v>0.5256502687689637</v>
       </c>
       <c r="G11">
-        <v>0.53216968210152071</v>
+        <v>0.5282446392054111</v>
       </c>
       <c r="H11">
-        <v>0.54494583156955401</v>
+        <v>0.5237565528279667</v>
       </c>
       <c r="I11">
-        <v>0.53275405832290279</v>
+        <v>0.5382288540679339</v>
       </c>
       <c r="J11">
-        <v>0.51518505528863345</v>
+        <v>0.5252506778932929</v>
       </c>
       <c r="K11">
-        <v>0.47844246230318749</v>
+        <v>0.5080076408864449</v>
       </c>
       <c r="L11">
-        <v>0.42047365165354877</v>
+        <v>0.4714790991579046</v>
       </c>
       <c r="M11">
-        <v>0.41640694407355883</v>
+        <v>0.4152475323240354</v>
       </c>
       <c r="N11">
-        <v>0.45407920673150137</v>
+        <v>0.4117004647927042</v>
       </c>
       <c r="O11">
-        <v>0.48914995074402939</v>
+        <v>0.4508999655716992</v>
       </c>
       <c r="P11">
-        <v>0.47942382127043648</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
+        <v>0.485875200762513</v>
+      </c>
+      <c r="Q11">
+        <v>0.4752903842042958</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>0.49490970542930779</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C12">
-        <v>0.50513996723538956</v>
+        <v>0.5005612370803739</v>
       </c>
       <c r="D12">
-        <v>0.53193915402755421</v>
+        <v>0.512170975821079</v>
       </c>
       <c r="E12">
-        <v>0.55617642261615108</v>
+        <v>0.5402240708545359</v>
       </c>
       <c r="F12">
-        <v>0.55961532921881607</v>
+        <v>0.5612906480883819</v>
       </c>
       <c r="G12">
-        <v>0.5589331292325338</v>
+        <v>0.5634830998791246</v>
       </c>
       <c r="H12">
-        <v>0.55408654256871348</v>
+        <v>0.5640500494720779</v>
       </c>
       <c r="I12">
-        <v>0.52980854500105323</v>
+        <v>0.5557669116278132</v>
       </c>
       <c r="J12">
-        <v>0.49092245394569167</v>
+        <v>0.5352127725161964</v>
       </c>
       <c r="K12">
-        <v>0.44015928013943201</v>
+        <v>0.4944014516510481</v>
       </c>
       <c r="L12">
-        <v>0.38779411060456581</v>
+        <v>0.4491112535294811</v>
       </c>
       <c r="M12">
-        <v>0.35157900308503942</v>
+        <v>0.3958429497564396</v>
       </c>
       <c r="N12">
-        <v>0.36329038113223538</v>
+        <v>0.3666124950925809</v>
       </c>
       <c r="O12">
-        <v>0.37727463772755843</v>
+        <v>0.3797317196143963</v>
       </c>
       <c r="P12">
-        <v>0.3676609747453477</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>27</v>
+        <v>0.3903734140796845</v>
+      </c>
+      <c r="Q12">
+        <v>0.3822562965717374</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>0.49560192810780329</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C13">
-        <v>0.5066523459620037</v>
+        <v>0.4941473798966715</v>
       </c>
       <c r="D13">
-        <v>0.51580277711700795</v>
+        <v>0.5061764077632248</v>
       </c>
       <c r="E13">
-        <v>0.52675921984341456</v>
+        <v>0.5121274058158689</v>
       </c>
       <c r="F13">
-        <v>0.5355206648777856</v>
+        <v>0.5240541698195302</v>
       </c>
       <c r="G13">
-        <v>0.5277497684017205</v>
+        <v>0.5307974668132373</v>
       </c>
       <c r="H13">
-        <v>0.52340963464355084</v>
+        <v>0.5235911151247482</v>
       </c>
       <c r="I13">
-        <v>0.49600390312273152</v>
+        <v>0.5188434872650233</v>
       </c>
       <c r="J13">
-        <v>0.47027654395246049</v>
+        <v>0.4922046658420032</v>
       </c>
       <c r="K13">
-        <v>0.41381476040639248</v>
+        <v>0.467042987517008</v>
       </c>
       <c r="L13">
-        <v>0.38768556017110212</v>
+        <v>0.4093927359413676</v>
       </c>
       <c r="M13">
-        <v>0.3690183916520422</v>
+        <v>0.3862506291920478</v>
       </c>
       <c r="N13">
-        <v>0.3424736321764828</v>
+        <v>0.3649053632192192</v>
       </c>
       <c r="O13">
-        <v>0.31285381746273933</v>
+        <v>0.3410657626725482</v>
       </c>
       <c r="P13">
-        <v>0.2575961903929046</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>28</v>
+        <v>0.3093302146248648</v>
+      </c>
+      <c r="Q13">
+        <v>0.263944940646353</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>0.35475792977148329</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C14">
-        <v>0.48666370982536189</v>
+        <v>0.3549879963938744</v>
       </c>
       <c r="D14">
-        <v>0.54574281065926367</v>
+        <v>0.4865873336312975</v>
       </c>
       <c r="E14">
-        <v>0.58059993376760988</v>
+        <v>0.5451915095253654</v>
       </c>
       <c r="F14">
-        <v>0.58680497570347212</v>
+        <v>0.5807361967442387</v>
       </c>
       <c r="G14">
-        <v>0.58620030018611369</v>
+        <v>0.5878024805319406</v>
       </c>
       <c r="H14">
-        <v>0.57533907088765934</v>
+        <v>0.5857476270662002</v>
       </c>
       <c r="I14">
-        <v>0.58033909003291839</v>
+        <v>0.5762224956518402</v>
       </c>
       <c r="J14">
-        <v>0.55616150729256653</v>
+        <v>0.5789499613702228</v>
       </c>
       <c r="K14">
-        <v>0.5157735644783169</v>
+        <v>0.5523343922275766</v>
       </c>
       <c r="L14">
-        <v>0.50298439884575141</v>
+        <v>0.5141201213948228</v>
       </c>
       <c r="M14">
-        <v>0.46849219096248118</v>
+        <v>0.4995606443742123</v>
       </c>
       <c r="N14">
-        <v>0.4591749265927666</v>
+        <v>0.4663880314953783</v>
       </c>
       <c r="O14">
-        <v>0.47359080024285072</v>
+        <v>0.4624866941236258</v>
       </c>
       <c r="P14">
-        <v>0.50304071419093044</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>29</v>
+        <v>0.4755752187712418</v>
+      </c>
+      <c r="Q14">
+        <v>0.5056176909523865</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>0.35438062459399677</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C15">
-        <v>0.48605392175920342</v>
+        <v>0.3519621701501007</v>
       </c>
       <c r="D15">
-        <v>0.54527993402859043</v>
+        <v>0.4822529604471648</v>
       </c>
       <c r="E15">
-        <v>0.57877593377067038</v>
+        <v>0.542184627652283</v>
       </c>
       <c r="F15">
-        <v>0.58551268950375768</v>
+        <v>0.578344854782892</v>
       </c>
       <c r="G15">
-        <v>0.58309462351512342</v>
+        <v>0.5862346653947058</v>
       </c>
       <c r="H15">
-        <v>0.57595651091593592</v>
+        <v>0.5843871108696279</v>
       </c>
       <c r="I15">
-        <v>0.57952664943727505</v>
+        <v>0.5778345397502868</v>
       </c>
       <c r="J15">
-        <v>0.55645704145302954</v>
+        <v>0.580368000286548</v>
       </c>
       <c r="K15">
-        <v>0.5179164452388676</v>
+        <v>0.5584034723780903</v>
       </c>
       <c r="L15">
-        <v>0.51237475738040517</v>
+        <v>0.5215166694087017</v>
       </c>
       <c r="M15">
-        <v>0.47734129618657739</v>
+        <v>0.5108453411934942</v>
       </c>
       <c r="N15">
-        <v>0.47292050065195501</v>
+        <v>0.4750972602873909</v>
       </c>
       <c r="O15">
-        <v>0.48592850218077271</v>
+        <v>0.4728970616371827</v>
       </c>
       <c r="P15">
-        <v>0.51237542885772303</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
+        <v>0.4835945368985207</v>
+      </c>
+      <c r="Q15">
+        <v>0.5108868564827947</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>0.35623579000014871</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C16">
-        <v>0.48731535433126749</v>
+        <v>0.3529352924899422</v>
       </c>
       <c r="D16">
-        <v>0.54733022178458335</v>
+        <v>0.486302595963385</v>
       </c>
       <c r="E16">
-        <v>0.58292793730122994</v>
+        <v>0.5460905121208656</v>
       </c>
       <c r="F16">
-        <v>0.59003713263886759</v>
+        <v>0.5814371883997629</v>
       </c>
       <c r="G16">
-        <v>0.58519130932475283</v>
+        <v>0.5881598895837852</v>
       </c>
       <c r="H16">
-        <v>0.57891081978782144</v>
+        <v>0.5828793853821665</v>
       </c>
       <c r="I16">
-        <v>0.58127657185598181</v>
+        <v>0.5745798708459693</v>
       </c>
       <c r="J16">
-        <v>0.55770173385664068</v>
+        <v>0.5802093772420386</v>
       </c>
       <c r="K16">
-        <v>0.51892992689645945</v>
+        <v>0.5538507371924212</v>
       </c>
       <c r="L16">
-        <v>0.51121643455713617</v>
+        <v>0.5152676459716111</v>
       </c>
       <c r="M16">
-        <v>0.48244680140896068</v>
+        <v>0.5078665497460203</v>
       </c>
       <c r="N16">
-        <v>0.47302731327631659</v>
+        <v>0.4816516575256861</v>
       </c>
       <c r="O16">
-        <v>0.48032169530718682</v>
+        <v>0.4712959667265215</v>
       </c>
       <c r="P16">
-        <v>0.50199912411170777</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>31</v>
+        <v>0.4797250817121809</v>
+      </c>
+      <c r="Q16">
+        <v>0.5020762513867302</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>0.35279564936414848</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C17">
-        <v>0.48545197395995943</v>
+        <v>0.3509399383932449</v>
       </c>
       <c r="D17">
-        <v>0.54411137849562419</v>
+        <v>0.481932768559413</v>
       </c>
       <c r="E17">
-        <v>0.58108444344613885</v>
+        <v>0.5380202635389582</v>
       </c>
       <c r="F17">
-        <v>0.5881856211337616</v>
+        <v>0.5756072979490245</v>
       </c>
       <c r="G17">
-        <v>0.5851174379201014</v>
+        <v>0.5809667997254049</v>
       </c>
       <c r="H17">
-        <v>0.57669548271208027</v>
+        <v>0.579512148080347</v>
       </c>
       <c r="I17">
-        <v>0.58185446801967011</v>
+        <v>0.5689976103656051</v>
       </c>
       <c r="J17">
-        <v>0.55722208185773847</v>
+        <v>0.5726967483912299</v>
       </c>
       <c r="K17">
-        <v>0.52027871963310168</v>
+        <v>0.5467165532672984</v>
       </c>
       <c r="L17">
-        <v>0.51230732134697121</v>
+        <v>0.5071115420552154</v>
       </c>
       <c r="M17">
-        <v>0.49411815397791409</v>
+        <v>0.499899085020159</v>
       </c>
       <c r="N17">
-        <v>0.48755082833233132</v>
+        <v>0.4775667131667817</v>
       </c>
       <c r="O17">
-        <v>0.50641774158651554</v>
+        <v>0.4692306071589182</v>
       </c>
       <c r="P17">
-        <v>0.52092226822286158</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>32</v>
+        <v>0.4853826241148189</v>
+      </c>
+      <c r="Q17">
+        <v>0.5037406584879986</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>0.49766482961425829</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C18">
-        <v>0.50590793241966192</v>
+        <v>0.4972209602176128</v>
       </c>
       <c r="D18">
-        <v>0.52957214511646233</v>
+        <v>0.4981723445318595</v>
       </c>
       <c r="E18">
-        <v>0.55464464744211517</v>
+        <v>0.5202518212326948</v>
       </c>
       <c r="F18">
-        <v>0.56508405795366579</v>
+        <v>0.5444040871215974</v>
       </c>
       <c r="G18">
-        <v>0.56141873043664892</v>
+        <v>0.5544400710380536</v>
       </c>
       <c r="H18">
-        <v>0.55798731946878466</v>
+        <v>0.5504647303738414</v>
       </c>
       <c r="I18">
-        <v>0.51619580350991101</v>
+        <v>0.5470978608429402</v>
       </c>
       <c r="J18">
-        <v>0.5047576979923577</v>
+        <v>0.5060308214948632</v>
       </c>
       <c r="K18">
-        <v>0.45905623868199757</v>
+        <v>0.4942455224959064</v>
       </c>
       <c r="L18">
-        <v>0.43236296480229552</v>
+        <v>0.4435576066744479</v>
       </c>
       <c r="M18">
-        <v>0.42249309700915189</v>
+        <v>0.4167907492438835</v>
       </c>
       <c r="N18">
-        <v>0.44364593556582849</v>
+        <v>0.4065981114260049</v>
       </c>
       <c r="O18">
-        <v>0.45369180300398382</v>
+        <v>0.4315680235063458</v>
       </c>
       <c r="P18">
-        <v>0.46399151468732103</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>33</v>
+        <v>0.4466100271715324</v>
+      </c>
+      <c r="Q18">
+        <v>0.4568792346896338</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>0.49822911122100072</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C19">
-        <v>0.50262951602884054</v>
+        <v>0.4990632931050734</v>
       </c>
       <c r="D19">
-        <v>0.51694935295499622</v>
+        <v>0.5010937563394788</v>
       </c>
       <c r="E19">
-        <v>0.53503978995256884</v>
+        <v>0.5114377500986984</v>
       </c>
       <c r="F19">
-        <v>0.56197563807459161</v>
+        <v>0.5303493475070982</v>
       </c>
       <c r="G19">
-        <v>0.55181411245406009</v>
+        <v>0.5616900551073305</v>
       </c>
       <c r="H19">
-        <v>0.53943985125112759</v>
+        <v>0.5519421061465566</v>
       </c>
       <c r="I19">
-        <v>0.50814878823792464</v>
+        <v>0.5424778847762389</v>
       </c>
       <c r="J19">
-        <v>0.45671265820374851</v>
+        <v>0.5100589199457647</v>
       </c>
       <c r="K19">
-        <v>0.43271761569210421</v>
+        <v>0.4606538467442637</v>
       </c>
       <c r="L19">
-        <v>0.4122748761783554</v>
+        <v>0.4334158422507027</v>
       </c>
       <c r="M19">
-        <v>0.42325429171699641</v>
+        <v>0.4122469577345741</v>
       </c>
       <c r="N19">
-        <v>0.43075027936201599</v>
+        <v>0.4213274657890521</v>
       </c>
       <c r="O19">
-        <v>0.44394870340287967</v>
+        <v>0.4304426628289337</v>
       </c>
       <c r="P19">
-        <v>0.4277619532738674</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>34</v>
+        <v>0.4424860493403626</v>
+      </c>
+      <c r="Q19">
+        <v>0.4260765098760079</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>0.50033358770074965</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C20">
-        <v>0.50386341848171912</v>
+        <v>0.5005003736110315</v>
       </c>
       <c r="D20">
-        <v>0.52527284810121788</v>
+        <v>0.5089145058650256</v>
       </c>
       <c r="E20">
-        <v>0.54071433159488624</v>
+        <v>0.5293712301947585</v>
       </c>
       <c r="F20">
-        <v>0.55472244862230835</v>
+        <v>0.5475757828457033</v>
       </c>
       <c r="G20">
-        <v>0.55862550192771043</v>
+        <v>0.5590081417550886</v>
       </c>
       <c r="H20">
-        <v>0.53584297634468825</v>
+        <v>0.5594379889507625</v>
       </c>
       <c r="I20">
-        <v>0.51347828125781125</v>
+        <v>0.5393431896891987</v>
       </c>
       <c r="J20">
-        <v>0.46139725086511041</v>
+        <v>0.5208759130410997</v>
       </c>
       <c r="K20">
-        <v>0.42965215568317422</v>
+        <v>0.4685464302031142</v>
       </c>
       <c r="L20">
-        <v>0.44271585520344708</v>
+        <v>0.4351723127623848</v>
       </c>
       <c r="M20">
-        <v>0.47007309728029451</v>
+        <v>0.4408481672488269</v>
       </c>
       <c r="N20">
-        <v>0.46995795863015538</v>
+        <v>0.4679473782030641</v>
       </c>
       <c r="O20">
-        <v>0.50259156675826366</v>
+        <v>0.4701803277054329</v>
       </c>
       <c r="P20">
-        <v>0.4805487972466132</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>35</v>
+        <v>0.4959488860642037</v>
+      </c>
+      <c r="Q20">
+        <v>0.4751421158823158</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>0.43536736033423301</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C21">
-        <v>0.49455280111675759</v>
+        <v>0.4379953087405391</v>
       </c>
       <c r="D21">
-        <v>0.49677249633805892</v>
+        <v>0.4960286677157131</v>
       </c>
       <c r="E21">
-        <v>0.51688845433305108</v>
+        <v>0.495186839351771</v>
       </c>
       <c r="F21">
-        <v>0.53167901538914231</v>
+        <v>0.5176527314180848</v>
       </c>
       <c r="G21">
-        <v>0.53091618807612972</v>
+        <v>0.5253767069373536</v>
       </c>
       <c r="H21">
-        <v>0.46637486640099041</v>
+        <v>0.5328060666672093</v>
       </c>
       <c r="I21">
-        <v>0.43280433453757611</v>
+        <v>0.4625228406544887</v>
       </c>
       <c r="J21">
-        <v>0.41572424920957468</v>
+        <v>0.4313263560521885</v>
       </c>
       <c r="K21">
-        <v>0.38054779923942789</v>
+        <v>0.4204391580700721</v>
       </c>
       <c r="L21">
-        <v>0.35068171848744278</v>
+        <v>0.3886367058754894</v>
       </c>
       <c r="M21">
-        <v>0.29194896498051481</v>
+        <v>0.3564392083045081</v>
       </c>
       <c r="N21">
-        <v>0.23837985719668039</v>
+        <v>0.2988467862533219</v>
       </c>
       <c r="O21">
-        <v>0.17176514278643071</v>
+        <v>0.2483935958142937</v>
       </c>
       <c r="P21">
-        <v>6.3463795498211059E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>36</v>
+        <v>0.1907454015058232</v>
+      </c>
+      <c r="Q21">
+        <v>0.08967386918446957</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>0.43744705652928539</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C22">
-        <v>0.49477211643924601</v>
+        <v>0.4362234907776945</v>
       </c>
       <c r="D22">
-        <v>0.49370110983693238</v>
+        <v>0.4945939616502368</v>
       </c>
       <c r="E22">
-        <v>0.51163264376015638</v>
+        <v>0.4945760091834498</v>
       </c>
       <c r="F22">
-        <v>0.52605474085369175</v>
+        <v>0.5142355941346282</v>
       </c>
       <c r="G22">
-        <v>0.54089445403358472</v>
+        <v>0.5301044923469477</v>
       </c>
       <c r="H22">
-        <v>0.46671425211563128</v>
+        <v>0.5452576582167732</v>
       </c>
       <c r="I22">
-        <v>0.43928725144600989</v>
+        <v>0.4768290051278395</v>
       </c>
       <c r="J22">
-        <v>0.42927326020173601</v>
+        <v>0.4486355103809403</v>
       </c>
       <c r="K22">
-        <v>0.40806659980339499</v>
+        <v>0.4393648312264374</v>
       </c>
       <c r="L22">
-        <v>0.36318365349405202</v>
+        <v>0.412936733256718</v>
       </c>
       <c r="M22">
-        <v>0.30496744431658579</v>
+        <v>0.3705164260758033</v>
       </c>
       <c r="N22">
-        <v>0.26764167351960377</v>
+        <v>0.3133232388650319</v>
       </c>
       <c r="O22">
-        <v>0.1918492124320279</v>
+        <v>0.2769898529074401</v>
       </c>
       <c r="P22">
-        <v>8.9350052964228974E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>37</v>
+        <v>0.201580495219517</v>
+      </c>
+      <c r="Q22">
+        <v>0.09910614386219396</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>0.49268337708515669</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C23">
-        <v>0.49281667734417461</v>
+        <v>0.4932154977398217</v>
       </c>
       <c r="D23">
-        <v>0.52787465666737865</v>
+        <v>0.4952853348548907</v>
       </c>
       <c r="E23">
-        <v>0.54005887091947535</v>
+        <v>0.5253999389190013</v>
       </c>
       <c r="F23">
-        <v>0.50380996410798118</v>
+        <v>0.5436505344200818</v>
       </c>
       <c r="G23">
-        <v>0.39775701170860472</v>
+        <v>0.5075693934719288</v>
       </c>
       <c r="H23">
-        <v>0.34610495452842172</v>
+        <v>0.3982241533669422</v>
       </c>
       <c r="I23">
-        <v>0.33273370615979969</v>
+        <v>0.3408117702381645</v>
       </c>
       <c r="J23">
-        <v>0.28856992470763593</v>
+        <v>0.3267007333913745</v>
       </c>
       <c r="K23">
-        <v>0.2403864379953739</v>
+        <v>0.2812948104994528</v>
       </c>
       <c r="L23">
-        <v>0.1735650362325685</v>
+        <v>0.2309802230181</v>
       </c>
       <c r="M23">
-        <v>7.9505318974110659E-2</v>
+        <v>0.1704454018372319</v>
       </c>
       <c r="N23">
-        <v>-5.3390966678262743E-4</v>
+        <v>0.08562317547413942</v>
       </c>
       <c r="O23">
-        <v>-6.7720237183864621E-2</v>
+        <v>0.001886248404345564</v>
       </c>
       <c r="P23">
-        <v>-0.19488303264239451</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>38</v>
+        <v>-0.06063814453257235</v>
+      </c>
+      <c r="Q23">
+        <v>-0.1917588951573055</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>0.13837930259237111</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C24">
-        <v>0.1152352851125017</v>
+        <v>0.548578291336306</v>
       </c>
       <c r="D24">
-        <v>0.15321988441520079</v>
+        <v>0.608813820294038</v>
       </c>
       <c r="E24">
-        <v>7.008578801064852E-2</v>
+        <v>0.6378830291951918</v>
       </c>
       <c r="F24">
-        <v>-6.4034759570696126E-2</v>
+        <v>0.6598100011629447</v>
       </c>
       <c r="G24">
-        <v>-7.2934302228269077E-2</v>
+        <v>0.6598377710567297</v>
       </c>
       <c r="H24">
-        <v>-0.1128657393739768</v>
+        <v>0.6675423789569133</v>
       </c>
       <c r="I24">
-        <v>-0.1982713435930179</v>
+        <v>0.6633824803854598</v>
       </c>
       <c r="J24">
-        <v>-0.26525019003469452</v>
+        <v>0.6568288653893257</v>
       </c>
       <c r="K24">
-        <v>-0.2828851852444364</v>
+        <v>0.6320794592301816</v>
       </c>
       <c r="L24">
-        <v>-0.33246225222057368</v>
+        <v>0.5951485178511674</v>
       </c>
       <c r="M24">
-        <v>-0.35776803469766028</v>
+        <v>0.5650536816880758</v>
       </c>
       <c r="N24">
-        <v>-0.48358735521531782</v>
+        <v>0.5061303567250856</v>
       </c>
       <c r="O24">
-        <v>-0.5306892745894608</v>
+        <v>0.4447977523166813</v>
       </c>
       <c r="P24">
-        <v>-0.57933097108602793</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>39</v>
+        <v>0.3672148732574768</v>
+      </c>
+      <c r="Q24">
+        <v>0.2816008615297557</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>0.1004652827545712</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C25">
-        <v>8.5707230246005711E-2</v>
+        <v>0.5437785033567369</v>
       </c>
       <c r="D25">
-        <v>6.6474103185907255E-2</v>
+        <v>0.6107954852552527</v>
       </c>
       <c r="E25">
-        <v>4.8635574504234627E-2</v>
+        <v>0.654549283176491</v>
       </c>
       <c r="F25">
-        <v>-1.109272623540526E-3</v>
+        <v>0.6906414739399415</v>
       </c>
       <c r="G25">
-        <v>-0.13368486836823459</v>
+        <v>0.7057708506634573</v>
       </c>
       <c r="H25">
-        <v>-0.18449271499827721</v>
+        <v>0.7138186862308523</v>
       </c>
       <c r="I25">
-        <v>-0.25470762883319698</v>
+        <v>0.7085862876941255</v>
       </c>
       <c r="J25">
-        <v>-0.29934854817146272</v>
+        <v>0.678916239017847</v>
       </c>
       <c r="K25">
-        <v>-0.36634852819872182</v>
+        <v>0.6746477880840378</v>
       </c>
       <c r="L25">
-        <v>-0.44917755682616239</v>
+        <v>0.6760084233914604</v>
       </c>
       <c r="M25">
-        <v>-0.52811830113693681</v>
+        <v>0.6293743144913273</v>
       </c>
       <c r="N25">
-        <v>-0.60380110706173451</v>
+        <v>0.6029133986282538</v>
       </c>
       <c r="O25">
-        <v>-0.66283853935827963</v>
+        <v>0.5437765062905695</v>
       </c>
       <c r="P25">
-        <v>-0.69657487765616888</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>40</v>
+        <v>0.5011290894009762</v>
+      </c>
+      <c r="Q25">
+        <v>0.4034009023893351</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>0.10106822151843051</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C26">
-        <v>9.1243734611720279E-2</v>
+        <v>0.5595635835464632</v>
       </c>
       <c r="D26">
-        <v>0.1054587096658214</v>
+        <v>0.5920865766802992</v>
       </c>
       <c r="E26">
-        <v>0.1049842546293431</v>
+        <v>0.6408296956611327</v>
       </c>
       <c r="F26">
-        <v>4.5963514333940733E-2</v>
+        <v>0.6730694491350324</v>
       </c>
       <c r="G26">
-        <v>2.8290589045167191E-3</v>
+        <v>0.6754590013406285</v>
       </c>
       <c r="H26">
-        <v>-0.10767749747947671</v>
+        <v>0.6840852697263705</v>
       </c>
       <c r="I26">
-        <v>-0.14188775452395569</v>
+        <v>0.68807434358582</v>
       </c>
       <c r="J26">
-        <v>-9.370487057187521E-2</v>
+        <v>0.677108812689737</v>
       </c>
       <c r="K26">
-        <v>-7.9919024466599445E-2</v>
+        <v>0.6327011510975309</v>
       </c>
       <c r="L26">
-        <v>-0.1208321117747742</v>
+        <v>0.6236532686869506</v>
       </c>
       <c r="M26">
-        <v>-0.327751488427445</v>
+        <v>0.5699177817812033</v>
       </c>
       <c r="N26">
-        <v>-0.26908909806025921</v>
+        <v>0.5353753902455848</v>
       </c>
       <c r="O26">
-        <v>-0.25760458807349851</v>
+        <v>0.4788586827172589</v>
       </c>
       <c r="P26">
-        <v>-0.24663308592258279</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>41</v>
+        <v>0.4001460008938739</v>
+      </c>
+      <c r="Q26">
+        <v>0.3332543514730669</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>7.0310315401076406E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C27">
-        <v>5.3144163194754283E-2</v>
+        <v>0.5584854774407539</v>
       </c>
       <c r="D27">
-        <v>3.5438092188961899E-2</v>
+        <v>0.5903306827081933</v>
       </c>
       <c r="E27">
-        <v>9.5743312360310681E-2</v>
+        <v>0.6389546630889489</v>
       </c>
       <c r="F27">
-        <v>2.1778541424050619E-2</v>
+        <v>0.6717421069460513</v>
       </c>
       <c r="G27">
-        <v>-6.3297933090391773E-3</v>
+        <v>0.6716454330741296</v>
       </c>
       <c r="H27">
-        <v>4.9994345132552263E-2</v>
+        <v>0.6797301845320282</v>
       </c>
       <c r="I27">
-        <v>-2.8063860016616909E-2</v>
+        <v>0.6808583902161623</v>
       </c>
       <c r="J27">
-        <v>-7.0960304108662109E-2</v>
+        <v>0.6729765324751837</v>
       </c>
       <c r="K27">
-        <v>-0.1318092827204935</v>
+        <v>0.6344919433780218</v>
       </c>
       <c r="L27">
-        <v>-0.2191042226044955</v>
+        <v>0.6068906279013214</v>
       </c>
       <c r="M27">
-        <v>-0.27545801939364872</v>
+        <v>0.5629300209436279</v>
       </c>
       <c r="N27">
-        <v>-0.17233110161569939</v>
+        <v>0.5164548658260002</v>
       </c>
       <c r="O27">
-        <v>-0.23797968967426739</v>
+        <v>0.5000374868360133</v>
       </c>
       <c r="P27">
-        <v>-0.26750937355417331</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>42</v>
+        <v>0.503074473862972</v>
+      </c>
+      <c r="Q27">
+        <v>0.450605254095491</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>0.54874472947594555</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C28">
-        <v>0.61010652457272896</v>
+        <v>0.5424762069400243</v>
       </c>
       <c r="D28">
-        <v>0.64109613918081998</v>
+        <v>0.6084618086883722</v>
       </c>
       <c r="E28">
-        <v>0.66416917803411946</v>
+        <v>0.6514666082726718</v>
       </c>
       <c r="F28">
-        <v>0.66502791721142784</v>
+        <v>0.6884206469256288</v>
       </c>
       <c r="G28">
-        <v>0.66979335342136015</v>
+        <v>0.7044680234635815</v>
       </c>
       <c r="H28">
-        <v>0.66512088602321207</v>
+        <v>0.713134832433894</v>
       </c>
       <c r="I28">
-        <v>0.65693434795565997</v>
+        <v>0.7084494328000405</v>
       </c>
       <c r="J28">
-        <v>0.63179473387200469</v>
+        <v>0.6770789603027257</v>
       </c>
       <c r="K28">
-        <v>0.5965966648730624</v>
+        <v>0.6814666679839856</v>
       </c>
       <c r="L28">
-        <v>0.56788417082055409</v>
+        <v>0.6799920590951871</v>
       </c>
       <c r="M28">
-        <v>0.51114130827565984</v>
+        <v>0.6501636512666912</v>
       </c>
       <c r="N28">
-        <v>0.44828934462758618</v>
+        <v>0.6000906151793979</v>
       </c>
       <c r="O28">
-        <v>0.37393773763771082</v>
+        <v>0.578323710839152</v>
       </c>
       <c r="P28">
-        <v>0.28676930676429457</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>43</v>
+        <v>0.5659401736463364</v>
+      </c>
+      <c r="Q28">
+        <v>0.5280094745655547</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>0.54265912380465953</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C29">
-        <v>0.60928947650734</v>
+        <v>0.5438484228575569</v>
       </c>
       <c r="D29">
-        <v>0.65374506628015683</v>
+        <v>0.6096019854058987</v>
       </c>
       <c r="E29">
-        <v>0.6874624224567264</v>
+        <v>0.6545019902485459</v>
       </c>
       <c r="F29">
-        <v>0.70345282910528439</v>
+        <v>0.6906723355915734</v>
       </c>
       <c r="G29">
-        <v>0.71228016912182501</v>
+        <v>0.7061440005035485</v>
       </c>
       <c r="H29">
-        <v>0.70784868191928563</v>
+        <v>0.7148726563263827</v>
       </c>
       <c r="I29">
-        <v>0.67371123294555069</v>
+        <v>0.7101004424519781</v>
       </c>
       <c r="J29">
-        <v>0.67323552663968933</v>
+        <v>0.6846368167436517</v>
       </c>
       <c r="K29">
-        <v>0.67306111453294004</v>
+        <v>0.6856184436134304</v>
       </c>
       <c r="L29">
-        <v>0.63206682900021471</v>
+        <v>0.6859533808376875</v>
       </c>
       <c r="M29">
-        <v>0.60388276789270756</v>
+        <v>0.6621905074507562</v>
       </c>
       <c r="N29">
-        <v>0.54474296695095759</v>
+        <v>0.6138782972064585</v>
       </c>
       <c r="O29">
-        <v>0.50365401810686306</v>
+        <v>0.5868173669916769</v>
       </c>
       <c r="P29">
-        <v>0.40023640047709302</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>44</v>
+        <v>0.571239892715513</v>
+      </c>
+      <c r="Q29">
+        <v>0.5434287961324168</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>0.55887064876965686</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C30">
-        <v>0.59121093775977973</v>
+        <v>0.543766447051926</v>
       </c>
       <c r="D30">
-        <v>0.6393083188406683</v>
+        <v>0.6093654675588305</v>
       </c>
       <c r="E30">
-        <v>0.67118648670269454</v>
+        <v>0.6521984493962252</v>
       </c>
       <c r="F30">
-        <v>0.67501990234562848</v>
+        <v>0.6905522038677935</v>
       </c>
       <c r="G30">
-        <v>0.68382631929592619</v>
+        <v>0.7085025114767243</v>
       </c>
       <c r="H30">
-        <v>0.68463617630912521</v>
+        <v>0.7151366406047948</v>
       </c>
       <c r="I30">
-        <v>0.67518412187089294</v>
+        <v>0.713426561315619</v>
       </c>
       <c r="J30">
-        <v>0.63069506516833118</v>
+        <v>0.6840437343770651</v>
       </c>
       <c r="K30">
-        <v>0.62231637992993172</v>
+        <v>0.685752480352819</v>
       </c>
       <c r="L30">
-        <v>0.56942623418334903</v>
+        <v>0.6855455619217848</v>
       </c>
       <c r="M30">
-        <v>0.53339893189507237</v>
+        <v>0.6610676000616458</v>
       </c>
       <c r="N30">
-        <v>0.47533271457112342</v>
+        <v>0.6183675076495456</v>
       </c>
       <c r="O30">
-        <v>0.39668743343730267</v>
+        <v>0.5909807363189808</v>
       </c>
       <c r="P30">
-        <v>0.33019421741683092</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>45</v>
+        <v>0.5739940817555826</v>
+      </c>
+      <c r="Q30">
+        <v>0.5514772262789585</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>0.55943128163829625</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C31">
-        <v>0.59207706291993645</v>
+        <v>0.5438175829616426</v>
       </c>
       <c r="D31">
-        <v>0.6396506795246456</v>
+        <v>0.610931849246017</v>
       </c>
       <c r="E31">
-        <v>0.67083630181021825</v>
+        <v>0.6533222378062035</v>
       </c>
       <c r="F31">
-        <v>0.67219028597998121</v>
+        <v>0.6897334050910948</v>
       </c>
       <c r="G31">
-        <v>0.68227049717575783</v>
+        <v>0.7038540536131971</v>
       </c>
       <c r="H31">
-        <v>0.68217278675974768</v>
+        <v>0.7143924274679927</v>
       </c>
       <c r="I31">
-        <v>0.67365057465161682</v>
+        <v>0.7087539112419522</v>
       </c>
       <c r="J31">
-        <v>0.63506442742744562</v>
+        <v>0.6809969889232892</v>
       </c>
       <c r="K31">
-        <v>0.60733608738807321</v>
+        <v>0.6836575859700856</v>
       </c>
       <c r="L31">
-        <v>0.56604301967182835</v>
+        <v>0.6855463619836867</v>
       </c>
       <c r="M31">
-        <v>0.51874461793059046</v>
+        <v>0.6646812881951586</v>
       </c>
       <c r="N31">
-        <v>0.50176225468930225</v>
+        <v>0.6269418066270644</v>
       </c>
       <c r="O31">
-        <v>0.50335681050477132</v>
+        <v>0.5985357195163326</v>
       </c>
       <c r="P31">
-        <v>0.45304122532480889</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>46</v>
+        <v>0.5816203845816162</v>
+      </c>
+      <c r="Q31">
+        <v>0.5744675259554737</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>0.54387872840544049</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C32">
-        <v>0.61023210834648312</v>
+        <v>0.5464039521289409</v>
       </c>
       <c r="D32">
-        <v>0.65445731123843109</v>
+        <v>0.6130648049225448</v>
       </c>
       <c r="E32">
-        <v>0.68934781653930055</v>
+        <v>0.657492262467149</v>
       </c>
       <c r="F32">
-        <v>0.70284325630841671</v>
+        <v>0.6912345981729877</v>
       </c>
       <c r="G32">
-        <v>0.71192948857146854</v>
+        <v>0.7070461715462836</v>
       </c>
       <c r="H32">
-        <v>0.70587343147855086</v>
+        <v>0.7144392038811763</v>
       </c>
       <c r="I32">
-        <v>0.67697618194455567</v>
+        <v>0.710930562533883</v>
       </c>
       <c r="J32">
-        <v>0.68010268293746845</v>
+        <v>0.6819575111384001</v>
       </c>
       <c r="K32">
-        <v>0.67979492909689243</v>
+        <v>0.6828232799649956</v>
       </c>
       <c r="L32">
-        <v>0.65314635788802478</v>
+        <v>0.6810244224434664</v>
       </c>
       <c r="M32">
-        <v>0.60283956520067239</v>
+        <v>0.6441016892779787</v>
       </c>
       <c r="N32">
-        <v>0.57951584198915451</v>
+        <v>0.597394558249335</v>
       </c>
       <c r="O32">
-        <v>0.56365019767617297</v>
+        <v>0.5815211766551754</v>
       </c>
       <c r="P32">
-        <v>0.52478987424956347</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>47</v>
+        <v>0.5655944894198248</v>
+      </c>
+      <c r="Q32">
+        <v>0.5080029150512699</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>0.54501096739330379</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C33">
-        <v>0.61055067562404497</v>
+        <v>0.5431615994830358</v>
       </c>
       <c r="D33">
-        <v>0.65544515961632765</v>
+        <v>0.6085105765321932</v>
       </c>
       <c r="E33">
-        <v>0.69157594080824014</v>
+        <v>0.6514478929236415</v>
       </c>
       <c r="F33">
-        <v>0.70455476012410245</v>
+        <v>0.6882167018994422</v>
       </c>
       <c r="G33">
-        <v>0.71246890197386958</v>
+        <v>0.7026716305800559</v>
       </c>
       <c r="H33">
-        <v>0.70880947103224168</v>
+        <v>0.7110999797671174</v>
       </c>
       <c r="I33">
-        <v>0.68225056356733738</v>
+        <v>0.7065207086930497</v>
       </c>
       <c r="J33">
-        <v>0.68481075193016439</v>
+        <v>0.6747676299982248</v>
       </c>
       <c r="K33">
-        <v>0.68581297191526525</v>
+        <v>0.6746881047837768</v>
       </c>
       <c r="L33">
-        <v>0.66064029948205705</v>
+        <v>0.6724458717761638</v>
       </c>
       <c r="M33">
-        <v>0.61448612518910828</v>
+        <v>0.6392230610402948</v>
       </c>
       <c r="N33">
-        <v>0.59039312126868515</v>
+        <v>0.5886327953546935</v>
       </c>
       <c r="O33">
-        <v>0.57420762474062959</v>
+        <v>0.569740042195657</v>
       </c>
       <c r="P33">
-        <v>0.54535165374931083</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>48</v>
+        <v>0.557785636939956</v>
+      </c>
+      <c r="Q33">
+        <v>0.4999820944327584</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>0.54621654326524582</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C34">
-        <v>0.61159200367557565</v>
+        <v>0.5439276586741895</v>
       </c>
       <c r="D34">
-        <v>0.65447686060405186</v>
+        <v>0.6096196579968063</v>
       </c>
       <c r="E34">
-        <v>0.69158631195094744</v>
+        <v>0.6528380102136792</v>
       </c>
       <c r="F34">
-        <v>0.70632007396486629</v>
+        <v>0.689566504425455</v>
       </c>
       <c r="G34">
-        <v>0.71448837056104531</v>
+        <v>0.7053792077224437</v>
       </c>
       <c r="H34">
-        <v>0.70964570455155418</v>
+        <v>0.7141387821533939</v>
       </c>
       <c r="I34">
-        <v>0.68324780886767389</v>
+        <v>0.7105459426364845</v>
       </c>
       <c r="J34">
-        <v>0.68577047213533604</v>
+        <v>0.6824061234618576</v>
       </c>
       <c r="K34">
-        <v>0.68600745894543813</v>
+        <v>0.6813707611051092</v>
       </c>
       <c r="L34">
-        <v>0.66208463118644922</v>
+        <v>0.6810523581398813</v>
       </c>
       <c r="M34">
-        <v>0.62002190094555665</v>
+        <v>0.6474037713510699</v>
       </c>
       <c r="N34">
-        <v>0.59275715781908189</v>
+        <v>0.5936049745861015</v>
       </c>
       <c r="O34">
-        <v>0.5770513990646905</v>
+        <v>0.57507171378689</v>
       </c>
       <c r="P34">
-        <v>0.55000115474607314</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>49</v>
+        <v>0.562131767793819</v>
+      </c>
+      <c r="Q34">
+        <v>0.5162631862282406</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>0.54239091588430666</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C35">
-        <v>0.60880478274559069</v>
+        <v>0.5450156034504731</v>
       </c>
       <c r="D35">
-        <v>0.65344718894792309</v>
+        <v>0.6101939898097662</v>
       </c>
       <c r="E35">
-        <v>0.68966836934389253</v>
+        <v>0.6538326554396928</v>
       </c>
       <c r="F35">
-        <v>0.70474989308254421</v>
+        <v>0.6898788059885332</v>
       </c>
       <c r="G35">
-        <v>0.71505839444691921</v>
+        <v>0.7052540087337259</v>
       </c>
       <c r="H35">
-        <v>0.71064697321848358</v>
+        <v>0.7124345409369887</v>
       </c>
       <c r="I35">
-        <v>0.68279727935286127</v>
+        <v>0.7096920001067651</v>
       </c>
       <c r="J35">
-        <v>0.68564504466566845</v>
+        <v>0.6805457249220377</v>
       </c>
       <c r="K35">
-        <v>0.68718905606238467</v>
+        <v>0.6834038668645154</v>
       </c>
       <c r="L35">
-        <v>0.66473739836359824</v>
+        <v>0.6808157608688815</v>
       </c>
       <c r="M35">
-        <v>0.62382661420327279</v>
+        <v>0.6505876461985889</v>
       </c>
       <c r="N35">
-        <v>0.59587708225460989</v>
+        <v>0.60168816530474</v>
       </c>
       <c r="O35">
-        <v>0.57653765844575344</v>
+        <v>0.5780510432691058</v>
       </c>
       <c r="P35">
-        <v>0.56985999526077646</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>50</v>
+        <v>0.5699734335605948</v>
+      </c>
+      <c r="Q35">
+        <v>0.5264743170392618</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>0.54547571048102328</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C36">
-        <v>0.61256593638100154</v>
+        <v>0.5428748412563674</v>
       </c>
       <c r="D36">
-        <v>0.65634642666888243</v>
+        <v>0.6090137228435687</v>
       </c>
       <c r="E36">
-        <v>0.69283865512182818</v>
+        <v>0.6525689282632247</v>
       </c>
       <c r="F36">
-        <v>0.70765231173926624</v>
+        <v>0.6874868924627335</v>
       </c>
       <c r="G36">
-        <v>0.7156547787499643</v>
+        <v>0.7043972989116302</v>
       </c>
       <c r="H36">
-        <v>0.71282709695477497</v>
+        <v>0.7124810893382159</v>
       </c>
       <c r="I36">
-        <v>0.68660497334841619</v>
+        <v>0.7070663917287223</v>
       </c>
       <c r="J36">
-        <v>0.68554052975213575</v>
+        <v>0.6780532601263534</v>
       </c>
       <c r="K36">
-        <v>0.68512947809129399</v>
+        <v>0.679263836496076</v>
       </c>
       <c r="L36">
-        <v>0.64881304355493818</v>
+        <v>0.6807093403309152</v>
       </c>
       <c r="M36">
-        <v>0.60485122311393302</v>
+        <v>0.6578883135790049</v>
       </c>
       <c r="N36">
-        <v>0.5907212571070376</v>
+        <v>0.6217998151835554</v>
       </c>
       <c r="O36">
-        <v>0.57698565278343528</v>
+        <v>0.5949429054232256</v>
       </c>
       <c r="P36">
-        <v>0.51322892776995499</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>51</v>
+        <v>0.5796041924885386</v>
+      </c>
+      <c r="Q36">
+        <v>0.5647654224718661</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>0.54269332642131929</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C37">
-        <v>0.60838281836136487</v>
+        <v>0.5537908150915868</v>
       </c>
       <c r="D37">
-        <v>0.65322074985605116</v>
+        <v>0.5898375709882849</v>
       </c>
       <c r="E37">
-        <v>0.69009981178491719</v>
+        <v>0.6628065128771321</v>
       </c>
       <c r="F37">
-        <v>0.70447930165234773</v>
+        <v>0.6734578393516606</v>
       </c>
       <c r="G37">
-        <v>0.71339851352998607</v>
+        <v>0.6332215365178919</v>
       </c>
       <c r="H37">
-        <v>0.70952524473405287</v>
+        <v>0.618599227174742</v>
       </c>
       <c r="I37">
-        <v>0.68152410877248348</v>
+        <v>0.6339416603612946</v>
       </c>
       <c r="J37">
-        <v>0.68180598411337345</v>
+        <v>0.6113954224972838</v>
       </c>
       <c r="K37">
-        <v>0.68165499058289691</v>
+        <v>0.555216004515933</v>
       </c>
       <c r="L37">
-        <v>0.6468403664603356</v>
+        <v>0.5070808677819565</v>
       </c>
       <c r="M37">
-        <v>0.59714769981717963</v>
+        <v>0.4678418121862337</v>
       </c>
       <c r="N37">
-        <v>0.57888182297721191</v>
+        <v>0.4324919781304142</v>
       </c>
       <c r="O37">
-        <v>0.56602043865433149</v>
+        <v>0.406551841999317</v>
       </c>
       <c r="P37">
-        <v>0.50859252096424024</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>52</v>
+        <v>0.3739541954000061</v>
+      </c>
+      <c r="Q37">
+        <v>0.3528523203407897</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>0.54409028112192726</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C38">
-        <v>0.60959198609684195</v>
+        <v>0.5565812020733814</v>
       </c>
       <c r="D38">
-        <v>0.65129235583034961</v>
+        <v>0.6058428557269687</v>
       </c>
       <c r="E38">
-        <v>0.68856842732739154</v>
+        <v>0.6684746625603313</v>
       </c>
       <c r="F38">
-        <v>0.70413557860343057</v>
+        <v>0.6713745803220994</v>
       </c>
       <c r="G38">
-        <v>0.71136254350926198</v>
+        <v>0.64515937561019</v>
       </c>
       <c r="H38">
-        <v>0.70439696628321091</v>
+        <v>0.6166042384106427</v>
       </c>
       <c r="I38">
-        <v>0.67655655385733027</v>
+        <v>0.655709070151255</v>
       </c>
       <c r="J38">
-        <v>0.67992700039439458</v>
+        <v>0.6294370386951101</v>
       </c>
       <c r="K38">
-        <v>0.67884884003457679</v>
+        <v>0.5913806172136529</v>
       </c>
       <c r="L38">
-        <v>0.64819360301445428</v>
+        <v>0.5640723897203214</v>
       </c>
       <c r="M38">
-        <v>0.59597083611695179</v>
+        <v>0.5468627472746622</v>
       </c>
       <c r="N38">
-        <v>0.57479613300480958</v>
+        <v>0.5047498446372698</v>
       </c>
       <c r="O38">
-        <v>0.56104501900262227</v>
+        <v>0.4575258946003022</v>
       </c>
       <c r="P38">
-        <v>0.5143294709288625</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>53</v>
+        <v>0.4071403728212472</v>
+      </c>
+      <c r="Q38">
+        <v>0.3514541423253707</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>0.54248380046046296</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C39">
-        <v>0.60865896444448431</v>
+        <v>0.5595676553120387</v>
       </c>
       <c r="D39">
-        <v>0.65191879761657634</v>
+        <v>0.6118016997789196</v>
       </c>
       <c r="E39">
-        <v>0.68884458802753912</v>
+        <v>0.6725361273158822</v>
       </c>
       <c r="F39">
-        <v>0.70421998266499086</v>
+        <v>0.6751637199063882</v>
       </c>
       <c r="G39">
-        <v>0.71231037097319605</v>
+        <v>0.6573209080541259</v>
       </c>
       <c r="H39">
-        <v>0.70819749127530807</v>
+        <v>0.6395706650873951</v>
       </c>
       <c r="I39">
-        <v>0.68202200453149775</v>
+        <v>0.6614677548946829</v>
       </c>
       <c r="J39">
-        <v>0.68366062472814881</v>
+        <v>0.6358854614534321</v>
       </c>
       <c r="K39">
-        <v>0.68409148565495925</v>
+        <v>0.5985152810242766</v>
       </c>
       <c r="L39">
-        <v>0.6501878530751376</v>
+        <v>0.5566570722229285</v>
       </c>
       <c r="M39">
-        <v>0.59884635283724419</v>
+        <v>0.5253557351574371</v>
       </c>
       <c r="N39">
-        <v>0.5739631022635453</v>
+        <v>0.4782675327038969</v>
       </c>
       <c r="O39">
-        <v>0.56087595338000207</v>
+        <v>0.4525740668704462</v>
       </c>
       <c r="P39">
-        <v>0.51366305746007546</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>54</v>
+        <v>0.4408518919539868</v>
+      </c>
+      <c r="Q39">
+        <v>0.4060677659987991</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>0.5443221077111654</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C40">
-        <v>0.61140334239458516</v>
+        <v>0.5145006418459196</v>
       </c>
       <c r="D40">
-        <v>0.65503533781672896</v>
+        <v>0.5232388816247585</v>
       </c>
       <c r="E40">
-        <v>0.69080640735778787</v>
+        <v>0.5510468711828922</v>
       </c>
       <c r="F40">
-        <v>0.70398305847749787</v>
+        <v>0.5842863747191702</v>
       </c>
       <c r="G40">
-        <v>0.71519526065583727</v>
+        <v>0.6276144217611613</v>
       </c>
       <c r="H40">
-        <v>0.71012906132938036</v>
+        <v>0.6262044852826174</v>
       </c>
       <c r="I40">
-        <v>0.68255288746672038</v>
+        <v>0.590732417915779</v>
       </c>
       <c r="J40">
-        <v>0.68322075599994991</v>
+        <v>0.5727346384072561</v>
       </c>
       <c r="K40">
-        <v>0.68608676331404272</v>
+        <v>0.5435364564208242</v>
       </c>
       <c r="L40">
-        <v>0.66446647354910038</v>
+        <v>0.4962207034209832</v>
       </c>
       <c r="M40">
-        <v>0.62452666400935231</v>
+        <v>0.4253654441683686</v>
       </c>
       <c r="N40">
-        <v>0.59621584748028345</v>
+        <v>0.3452830311113121</v>
       </c>
       <c r="O40">
-        <v>0.58021243447879534</v>
+        <v>0.2888331662314366</v>
       </c>
       <c r="P40">
-        <v>0.56598385457978428</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>55</v>
+        <v>0.2197880017198929</v>
+      </c>
+      <c r="Q40">
+        <v>0.1499952623011594</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>0.55554700448183414</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C41">
-        <v>0.59481214257864679</v>
+        <v>0.4906422213587677</v>
       </c>
       <c r="D41">
-        <v>0.66283114628119744</v>
+        <v>0.518977746993121</v>
       </c>
       <c r="E41">
-        <v>0.67439103484802509</v>
+        <v>0.4713592264265432</v>
       </c>
       <c r="F41">
-        <v>0.6321488464735141</v>
+        <v>0.4099360190628362</v>
       </c>
       <c r="G41">
-        <v>0.62117728255586557</v>
+        <v>0.3462092722727486</v>
       </c>
       <c r="H41">
-        <v>0.63727156599137691</v>
+        <v>0.3550517178548022</v>
       </c>
       <c r="I41">
-        <v>0.61711548223974444</v>
+        <v>0.3895603905369702</v>
       </c>
       <c r="J41">
-        <v>0.56339630056822709</v>
+        <v>0.4049590863031048</v>
       </c>
       <c r="K41">
-        <v>0.51559618283687592</v>
+        <v>0.3992172659822095</v>
       </c>
       <c r="L41">
-        <v>0.47743052580978029</v>
+        <v>0.3455829673942373</v>
       </c>
       <c r="M41">
-        <v>0.44114145874954441</v>
+        <v>0.2536394030388162</v>
       </c>
       <c r="N41">
-        <v>0.41710808837806368</v>
+        <v>0.2064055378299129</v>
       </c>
       <c r="O41">
-        <v>0.38415373024155008</v>
+        <v>0.1754031821975598</v>
       </c>
       <c r="P41">
-        <v>0.36340303575451721</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>56</v>
+        <v>0.1287867013763035</v>
+      </c>
+      <c r="Q41">
+        <v>0.1246070538535057</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>0.55623775860621838</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C42">
-        <v>0.60765749031287197</v>
+        <v>0.4470434574992737</v>
       </c>
       <c r="D42">
-        <v>0.67097725271183628</v>
+        <v>0.5127395654041454</v>
       </c>
       <c r="E42">
-        <v>0.67511229887781765</v>
+        <v>0.4918536082457191</v>
       </c>
       <c r="F42">
-        <v>0.64559174380674733</v>
+        <v>0.4957861849846008</v>
       </c>
       <c r="G42">
-        <v>0.62375108416750824</v>
+        <v>0.4918380440017954</v>
       </c>
       <c r="H42">
-        <v>0.66304751309166288</v>
+        <v>0.5067727018920158</v>
       </c>
       <c r="I42">
-        <v>0.6403896975032598</v>
+        <v>0.5262697372383804</v>
       </c>
       <c r="J42">
-        <v>0.60323832718003412</v>
+        <v>0.4785681205657207</v>
       </c>
       <c r="K42">
-        <v>0.5776440363941403</v>
+        <v>0.4376255958069217</v>
       </c>
       <c r="L42">
-        <v>0.56010305714433428</v>
+        <v>0.3780375351507764</v>
       </c>
       <c r="M42">
-        <v>0.51894437191841591</v>
+        <v>0.3530923311990878</v>
       </c>
       <c r="N42">
-        <v>0.47369564536547998</v>
+        <v>0.3465264669028992</v>
       </c>
       <c r="O42">
-        <v>0.42160014521246469</v>
+        <v>0.3248813459061117</v>
       </c>
       <c r="P42">
-        <v>0.36741003192566107</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>57</v>
+        <v>0.3036632020348063</v>
+      </c>
+      <c r="Q42">
+        <v>0.2725975919442416</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>0.55810161213117238</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C43">
-        <v>0.6107026454905462</v>
+        <v>0.5158631648961218</v>
       </c>
       <c r="D43">
-        <v>0.6704596401654459</v>
+        <v>0.4874693733472127</v>
       </c>
       <c r="E43">
-        <v>0.67561299874990344</v>
+        <v>0.4707213280485322</v>
       </c>
       <c r="F43">
-        <v>0.65875598012798176</v>
+        <v>0.4372278165298539</v>
       </c>
       <c r="G43">
-        <v>0.63564157291004819</v>
+        <v>0.3847784435534067</v>
       </c>
       <c r="H43">
-        <v>0.65658519210493727</v>
+        <v>0.3917394062764493</v>
       </c>
       <c r="I43">
-        <v>0.629512014185442</v>
+        <v>0.4862951656858925</v>
       </c>
       <c r="J43">
-        <v>0.58978347388776142</v>
+        <v>0.5027338872499909</v>
       </c>
       <c r="K43">
-        <v>0.54614372427450331</v>
+        <v>0.4710407036852317</v>
       </c>
       <c r="L43">
-        <v>0.51420538164904994</v>
+        <v>0.4090916351339886</v>
       </c>
       <c r="M43">
-        <v>0.45488149811272149</v>
+        <v>0.3873513166559935</v>
       </c>
       <c r="N43">
-        <v>0.430847553442056</v>
+        <v>0.368699284973186</v>
       </c>
       <c r="O43">
-        <v>0.42039256455549689</v>
+        <v>0.3578710307989922</v>
       </c>
       <c r="P43">
-        <v>0.38224542246214382</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>58</v>
-      </c>
-      <c r="B44">
-        <v>0.51428358574879629</v>
-      </c>
-      <c r="C44">
-        <v>0.51618540672577273</v>
-      </c>
-      <c r="D44">
-        <v>0.54583290357820724</v>
-      </c>
-      <c r="E44">
-        <v>0.58115726672932488</v>
-      </c>
-      <c r="F44">
-        <v>0.62112993159373997</v>
-      </c>
-      <c r="G44">
-        <v>0.61983200298450747</v>
-      </c>
-      <c r="H44">
-        <v>0.57838328618130419</v>
-      </c>
-      <c r="I44">
-        <v>0.55953064842307587</v>
-      </c>
-      <c r="J44">
-        <v>0.53115763320923615</v>
-      </c>
-      <c r="K44">
-        <v>0.48209616101695862</v>
-      </c>
-      <c r="L44">
-        <v>0.41067168872402599</v>
-      </c>
-      <c r="M44">
-        <v>0.3280004192871166</v>
-      </c>
-      <c r="N44">
-        <v>0.26954951593613591</v>
-      </c>
-      <c r="O44">
-        <v>0.19863451271935609</v>
-      </c>
-      <c r="P44">
-        <v>0.12876007633470299</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>59</v>
-      </c>
-      <c r="B45">
-        <v>0.49192811968451672</v>
-      </c>
-      <c r="C45">
-        <v>0.52036995908459371</v>
-      </c>
-      <c r="D45">
-        <v>0.47418228992367017</v>
-      </c>
-      <c r="E45">
-        <v>0.41718958566283249</v>
-      </c>
-      <c r="F45">
-        <v>0.35950047213996761</v>
-      </c>
-      <c r="G45">
-        <v>0.36310108064170021</v>
-      </c>
-      <c r="H45">
-        <v>0.39538261903251037</v>
-      </c>
-      <c r="I45">
-        <v>0.40503563086244632</v>
-      </c>
-      <c r="J45">
-        <v>0.40592730050035281</v>
-      </c>
-      <c r="K45">
-        <v>0.34795238428333269</v>
-      </c>
-      <c r="L45">
-        <v>0.25963465335725611</v>
-      </c>
-      <c r="M45">
-        <v>0.2089824202674577</v>
-      </c>
-      <c r="N45">
-        <v>0.17542031568913119</v>
-      </c>
-      <c r="O45">
-        <v>0.12934878607467601</v>
-      </c>
-      <c r="P45">
-        <v>0.12676617247618421</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>60</v>
-      </c>
-      <c r="B46">
-        <v>0.44928299014085732</v>
-      </c>
-      <c r="C46">
-        <v>0.51541424991370854</v>
-      </c>
-      <c r="D46">
-        <v>0.49235370973684861</v>
-      </c>
-      <c r="E46">
-        <v>0.50007881953944422</v>
-      </c>
-      <c r="F46">
-        <v>0.4978490957571986</v>
-      </c>
-      <c r="G46">
-        <v>0.51379730811424384</v>
-      </c>
-      <c r="H46">
-        <v>0.53341329675453641</v>
-      </c>
-      <c r="I46">
-        <v>0.48948918185050039</v>
-      </c>
-      <c r="J46">
-        <v>0.44898669822205201</v>
-      </c>
-      <c r="K46">
-        <v>0.38771819997458118</v>
-      </c>
-      <c r="L46">
-        <v>0.36737363208909429</v>
-      </c>
-      <c r="M46">
-        <v>0.35959577604576282</v>
-      </c>
-      <c r="N46">
-        <v>0.33854719003512801</v>
-      </c>
-      <c r="O46">
-        <v>0.31317092226850129</v>
-      </c>
-      <c r="P46">
-        <v>0.28861375297635372</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>61</v>
-      </c>
-      <c r="B47">
-        <v>0.51939035798141875</v>
-      </c>
-      <c r="C47">
-        <v>0.49338147706636332</v>
-      </c>
-      <c r="D47">
-        <v>0.47846062741960532</v>
-      </c>
-      <c r="E47">
-        <v>0.44529359144546882</v>
-      </c>
-      <c r="F47">
-        <v>0.38997874881295519</v>
-      </c>
-      <c r="G47">
-        <v>0.40160264539317031</v>
-      </c>
-      <c r="H47">
-        <v>0.48942988580145907</v>
-      </c>
-      <c r="I47">
-        <v>0.50919972283923509</v>
-      </c>
-      <c r="J47">
-        <v>0.48214184288000878</v>
-      </c>
-      <c r="K47">
-        <v>0.41740294287425289</v>
-      </c>
-      <c r="L47">
-        <v>0.3965590717395841</v>
-      </c>
-      <c r="M47">
-        <v>0.38034468840500479</v>
-      </c>
-      <c r="N47">
-        <v>0.37470670799762662</v>
-      </c>
-      <c r="O47">
-        <v>0.37954548219555517</v>
-      </c>
-      <c r="P47">
-        <v>0.37835247630222019</v>
+        <v>0.3605087062136114</v>
+      </c>
+      <c r="Q43">
+        <v>0.364318922819189</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P47">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>